--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 14:39</t>
+          <t>2026-05-08 16:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05</t>
+          <t>2026-05-08 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Time_24h_Check" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:26</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -3881,102 +3881,8 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>71-5042</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>BigC</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="M75" s="5" t="n">
-        <v>15.43</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G76" s="6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K76" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L76" s="6" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="M76" s="6" t="n">
-        <v>20.37</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M76"/>
+  <autoFilter ref="A4:M74"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily_Time_24h_Check" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily_Time_24h_Check" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-05-26 13:09</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -608,16 +608,16 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>19.63</v>
+        <v>8.57</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>8.35</v>
+        <v>1.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>3.68</v>
+        <v>1.92</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
@@ -626,45 +626,45 @@
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>8.35</v>
+        <v>1.25</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>19.63</v>
+        <v>8.57</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>4.37</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>19.45</v>
+        <v>23.21</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7.42</v>
+        <v>1.61</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.9</v>
+        <v>19.9</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>10.13</v>
+        <v>1.7</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0</v>
@@ -673,27 +673,27 @@
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>7.42</v>
+        <v>1.61</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.9</v>
+        <v>19.9</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>19.45</v>
+        <v>23.21</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>4.55</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -702,63 +702,63 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>22.32</v>
+        <v>12.24</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>18.35</v>
+        <v>7.63</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>18.35</v>
+        <v>11.13</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1.27</v>
+        <v>11.7</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>22.32</v>
+        <v>25.28</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1.68</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>21.4</v>
+        <v>26.68</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>10.3</v>
+        <v>12.58</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>7.39</v>
+        <v>12.24</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3.71</v>
+        <v>1.86</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
@@ -767,45 +767,45 @@
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>10.3</v>
+        <v>12.58</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>7.39</v>
+        <v>12.24</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>21.4</v>
+        <v>26.68</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>2.6</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>24.87</v>
+        <v>37.14</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>18.91</v>
+        <v>34.14</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1.86</v>
+        <v>0.74</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
@@ -814,74 +814,74 @@
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>18.91</v>
+        <v>34.14</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1.86</v>
+        <v>0.74</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>24.87</v>
+        <v>37.14</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>-0.87</v>
+        <v>-13.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>24.43</v>
+        <v>26.65</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>14.47</v>
+        <v>18.52</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>5.98</v>
+        <v>6.08</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3.98</v>
+        <v>2.05</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>14.48</v>
+        <v>18.52</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>5.98</v>
+        <v>6.08</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>24.44</v>
+        <v>26.65</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>-0.44</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>71-8683</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -890,45 +890,45 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>22.24</v>
+        <v>14.58</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>14.81</v>
+        <v>6.09</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1.34</v>
+        <v>6.86</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>6.08</v>
+        <v>1.63</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>14.81</v>
+        <v>11.44</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1.34</v>
+        <v>6.86</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>22.24</v>
+        <v>19.93</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>1.76</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>12.48</v>
+        <v>22.68</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6.73</v>
+        <v>18.54</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
@@ -955,27 +955,27 @@
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>6.73</v>
+        <v>18.54</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>2.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>12.48</v>
+        <v>22.68</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>11.52</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>13.45</v>
+        <v>7.85</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>10.73</v>
+        <v>5.22</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
@@ -1002,45 +1002,45 @@
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>10.73</v>
+        <v>5.22</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>13.45</v>
+        <v>7.85</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>10.55</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>27.59</v>
+        <v>22.03</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>21.81</v>
+        <v>7.02</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>2.05</v>
+        <v>11.51</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3.73</v>
+        <v>3.49</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
@@ -1049,45 +1049,45 @@
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>21.81</v>
+        <v>7.02</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2.05</v>
+        <v>11.51</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>27.59</v>
+        <v>22.03</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>-3.59</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>21.8</v>
+        <v>25.02</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>18.98</v>
+        <v>14.52</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.78</v>
+        <v>8.73</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
@@ -1096,45 +1096,45 @@
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>18.98</v>
+        <v>14.52</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.78</v>
+        <v>8.73</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>21.8</v>
+        <v>25.02</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>2.2</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>22.38</v>
+        <v>24.32</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>15.37</v>
+        <v>13.41</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4.44</v>
+        <v>7.22</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2.57</v>
+        <v>3.69</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
@@ -1143,45 +1143,45 @@
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>15.37</v>
+        <v>13.41</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>4.44</v>
+        <v>7.22</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>22.38</v>
+        <v>24.32</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>1.62</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>21.23</v>
+        <v>10.63</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>10.99</v>
+        <v>7.9</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>2.72</v>
+        <v>1.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>7.52</v>
+        <v>1.62</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
@@ -1190,27 +1190,27 @@
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>10.99</v>
+        <v>7.9</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.72</v>
+        <v>1.1</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>21.23</v>
+        <v>10.63</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>2.77</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1219,16 +1219,16 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>17.3</v>
+        <v>7.88</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>9.279999999999999</v>
+        <v>4.78</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
@@ -1237,27 +1237,27 @@
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>9.279999999999999</v>
+        <v>4.78</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>17.3</v>
+        <v>7.88</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>6.7</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>5.98</v>
+        <v>15.89</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3.19</v>
+        <v>8.24</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.87</v>
+        <v>3.12</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.93</v>
+        <v>4.53</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -1284,27 +1284,27 @@
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>3.19</v>
+        <v>8.24</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.87</v>
+        <v>3.12</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>5.98</v>
+        <v>15.89</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>18.02</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>16.19</v>
+        <v>14.37</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>10.73</v>
+        <v>5.73</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3</v>
+        <v>4.94</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
@@ -1331,45 +1331,45 @@
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>10.73</v>
+        <v>5.73</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>16.19</v>
+        <v>14.37</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>7.81</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>10.46</v>
+        <v>30.03</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.75</v>
+        <v>18.47</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
@@ -1378,27 +1378,27 @@
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.75</v>
+        <v>18.47</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>10.46</v>
+        <v>30.03</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>13.54</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1407,16 +1407,16 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>8.16</v>
+        <v>19.22</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5.51</v>
+        <v>7.04</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.86</v>
+        <v>10.08</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -1425,27 +1425,27 @@
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>5.51</v>
+        <v>7.04</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.86</v>
+        <v>10.08</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>8.16</v>
+        <v>19.22</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>15.84</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1454,16 +1454,16 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>24.84</v>
+        <v>27.33</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>16.76</v>
+        <v>13.55</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1.92</v>
+        <v>10.43</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>6.16</v>
+        <v>3.36</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -1472,27 +1472,27 @@
         <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>16.76</v>
+        <v>13.55</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>1.92</v>
+        <v>10.43</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>24.84</v>
+        <v>27.33</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-0.84</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>25.8</v>
+        <v>18.8</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5.95</v>
+        <v>7.61</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.92</v>
+        <v>8.57</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>18.93</v>
+        <v>2.62</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
@@ -1519,45 +1519,45 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>5.95</v>
+        <v>7.61</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.92</v>
+        <v>8.57</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>25.8</v>
+        <v>18.8</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>-1.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>15.22</v>
+        <v>20.51</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>9.67</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1.74</v>
+        <v>5.55</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>3.82</v>
+        <v>5.58</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0</v>
@@ -1566,45 +1566,45 @@
         <v>0</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>9.67</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>1.74</v>
+        <v>5.55</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>15.22</v>
+        <v>20.51</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>11.67</v>
+        <v>15</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>6.19</v>
+        <v>5.78</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.61</v>
+        <v>6.55</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>3.87</v>
+        <v>2.68</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
@@ -1613,27 +1613,27 @@
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>6.19</v>
+        <v>5.78</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>1.61</v>
+        <v>6.55</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>11.67</v>
+        <v>15</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>12.33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>8.529999999999999</v>
+        <v>28.99</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5.37</v>
+        <v>11.22</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1.51</v>
+        <v>13.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.64</v>
+        <v>4.47</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
@@ -1660,27 +1660,27 @@
         <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>5.37</v>
+        <v>11.22</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1.51</v>
+        <v>13.3</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>8.529999999999999</v>
+        <v>28.99</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>15.47</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>14.23</v>
+        <v>23.27</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>8.93</v>
+        <v>12.14</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.89</v>
+        <v>6.63</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>4.41</v>
+        <v>4.49</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
@@ -1707,45 +1707,45 @@
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>8.93</v>
+        <v>12.14</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.89</v>
+        <v>6.63</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>14.23</v>
+        <v>23.27</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>9.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>19.53</v>
+        <v>7.24</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>3.4</v>
+        <v>0.78</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>8</v>
+        <v>1.73</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
@@ -1754,45 +1754,45 @@
         <v>0</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>4.73</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>3.4</v>
+        <v>0.78</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>19.53</v>
+        <v>7.24</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>4.47</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>10.9</v>
+        <v>19.15</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>4.22</v>
+        <v>14.59</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5.17</v>
+        <v>2.09</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
@@ -1801,27 +1801,27 @@
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>4.22</v>
+        <v>14.59</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>10.9</v>
+        <v>19.15</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>13.1</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1830,45 +1830,45 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>5.69</v>
+        <v>4.35</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2.44</v>
+        <v>1.79</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.9</v>
+        <v>0.66</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>2.44</v>
+        <v>1.79</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>1.5</v>
+        <v>0.66</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>6.29</v>
+        <v>4.35</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>17.71</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1877,63 +1877,63 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>22.06</v>
+        <v>10.66</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>12.91</v>
+        <v>7.47</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2.76</v>
+        <v>1.24</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>6.39</v>
+        <v>1.94</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>15.75</v>
+        <v>7.47</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2.76</v>
+        <v>1.24</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>24.9</v>
+        <v>10.66</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>-0.9</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>21.29</v>
+        <v>13.67</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>9.42</v>
+        <v>10.38</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>10.76</v>
+        <v>2</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>0</v>
@@ -1942,45 +1942,45 @@
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>9.42</v>
+        <v>10.38</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>21.29</v>
+        <v>13.67</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>2.71</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>7.82</v>
+        <v>27.88</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>2.71</v>
+        <v>18.42</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.15</v>
+        <v>5.43</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0</v>
@@ -1989,22 +1989,22 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2.71</v>
+        <v>18.42</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1.15</v>
+        <v>5.43</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>7.82</v>
+        <v>27.88</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>16.18</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2018,110 +2018,110 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>14.18</v>
+        <v>19.38</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>15.37</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>3.65</v>
+        <v>2.59</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>15.89</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>14.18</v>
+        <v>19.9</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>9.82</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>4.38</v>
+        <v>23.79</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>1.76</v>
+        <v>13.35</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.91</v>
+        <v>4.51</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1.71</v>
+        <v>5.93</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>9.960000000000001</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>11.71</v>
+        <v>13.35</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.91</v>
+        <v>4.51</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>14.33</v>
+        <v>23.79</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>9.67</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>18.31</v>
+        <v>27.17</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>7.45</v>
+        <v>19.94</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>2.09</v>
+        <v>3.18</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>8.76</v>
+        <v>4.05</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0</v>
@@ -2130,27 +2130,27 @@
         <v>0</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>7.45</v>
+        <v>19.94</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>2.09</v>
+        <v>3.18</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>18.31</v>
+        <v>27.17</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>5.69</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8683</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2159,45 +2159,45 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>10.78</v>
+        <v>0</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>10.78</v>
+        <v>1.49</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>13.22</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2206,63 +2206,63 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>19.15</v>
+        <v>29.48</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>6.78</v>
+        <v>13.75</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>2.33</v>
+        <v>12.64</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>10.05</v>
+        <v>3.09</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>6.78</v>
+        <v>13.75</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>3.9</v>
+        <v>12.64</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>20.73</v>
+        <v>29.48</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>3.27</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>11.75</v>
+        <v>6.48</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>5.23</v>
+        <v>2.52</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>4.35</v>
+        <v>2</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0</v>
@@ -2271,45 +2271,45 @@
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>5.23</v>
+        <v>2.52</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>11.75</v>
+        <v>6.48</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>12.25</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>10.63</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>6.2</v>
+        <v>4.33</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>1.37</v>
+        <v>2.96</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>3.06</v>
+        <v>1.91</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0</v>
@@ -2318,27 +2318,27 @@
         <v>0</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>6.2</v>
+        <v>4.33</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>1.37</v>
+        <v>2.96</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>10.63</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>13.37</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2347,16 +2347,16 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>16.66</v>
+        <v>20.76</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>4.07</v>
+        <v>12.25</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.72</v>
+        <v>5.48</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>10.87</v>
+        <v>3.03</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>0</v>
@@ -2365,45 +2365,45 @@
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>4.07</v>
+        <v>12.25</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>1.72</v>
+        <v>5.48</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>16.66</v>
+        <v>20.76</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>7.34</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>17.9</v>
+        <v>29.13</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>7.12</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>3.25</v>
+        <v>6.9</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>7.54</v>
+        <v>12.26</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>0</v>
@@ -2412,92 +2412,92 @@
         <v>0</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>7.12</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>3.25</v>
+        <v>6.9</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>17.9</v>
+        <v>29.13</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>6.1</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>18.33</v>
+        <v>0</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>9.77</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>2.2</v>
+        <v>0.37</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>18.33</v>
+        <v>0.37</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>5.67</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>13.86</v>
+        <v>22.59</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7.22</v>
+        <v>12.43</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>3.59</v>
+        <v>3.77</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>0</v>
@@ -2506,22 +2506,22 @@
         <v>0</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>7.22</v>
+        <v>12.43</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>13.86</v>
+        <v>22.59</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>10.14</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>10.46</v>
+        <v>20.29</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>4.52</v>
+        <v>10.52</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>2.1</v>
+        <v>6.05</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
@@ -2553,92 +2553,92 @@
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>4.52</v>
+        <v>10.52</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>2.1</v>
+        <v>6.05</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>10.46</v>
+        <v>20.29</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>13.54</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>18.87</v>
+        <v>21.67</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>5.08</v>
+        <v>6.68</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1.52</v>
+        <v>13.43</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>12.27</v>
+        <v>1.57</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>6.16</v>
+        <v>6.68</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>1.52</v>
+        <v>13.43</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>19.94</v>
+        <v>21.67</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>4.06</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>6.48</v>
+        <v>26.48</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>2.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.87</v>
+        <v>13.45</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0</v>
@@ -2647,45 +2647,45 @@
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>2.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>0.87</v>
+        <v>13.45</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>6.48</v>
+        <v>26.48</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>17.52</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>22.56</v>
+        <v>24.81</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>6.26</v>
+        <v>2.76</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>2.4</v>
+        <v>19.43</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>13.9</v>
+        <v>2.62</v>
       </c>
       <c r="H49" s="5" t="n">
         <v>0</v>
@@ -2694,27 +2694,27 @@
         <v>0</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>6.26</v>
+        <v>2.76</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>2.4</v>
+        <v>19.43</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>22.56</v>
+        <v>24.81</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>1.44</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2723,92 +2723,92 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>13.04</v>
+        <v>10.7</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>6.12</v>
+        <v>7.97</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>2.66</v>
+        <v>0.82</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>4.25</v>
+        <v>1.91</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>5.19</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>11.32</v>
+        <v>7.97</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>2.66</v>
+        <v>0.82</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>18.23</v>
+        <v>10.7</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>5.77</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>71-0558</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>0</v>
+        <v>15.1</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0.78</v>
+        <v>6.98</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.78</v>
+        <v>15.1</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>23.22</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -2817,16 +2817,16 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>46.15</v>
+        <v>29.14</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>13.66</v>
+        <v>22.27</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>21.94</v>
+        <v>3.37</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>10.55</v>
+        <v>3.51</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
@@ -2835,45 +2835,45 @@
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>13.66</v>
+        <v>22.27</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>21.94</v>
+        <v>3.37</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>46.15</v>
+        <v>29.14</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-22.15</v>
+        <v>-5.14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>51.18</v>
+        <v>25.37</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>21.28</v>
+        <v>13.71</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>22.22</v>
+        <v>8.08</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>7.68</v>
+        <v>3.58</v>
       </c>
       <c r="H53" s="5" t="n">
         <v>0</v>
@@ -2882,27 +2882,27 @@
         <v>0</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>21.28</v>
+        <v>13.71</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>22.22</v>
+        <v>8.08</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>51.18</v>
+        <v>25.37</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>-27.18</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -2911,139 +2911,139 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0</v>
+        <v>12.76</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>7.56</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>12.76</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>23.93</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>41.13</v>
+        <v>11.28</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>13.88</v>
+        <v>5.02</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>20.73</v>
+        <v>1.57</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>6.52</v>
+        <v>4.69</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>15.61</v>
+        <v>5.02</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>20.73</v>
+        <v>1.57</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>42.87</v>
+        <v>11.28</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>-18.87</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>34.62</v>
+        <v>18.92</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>10.41</v>
+        <v>13.65</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>18</v>
+        <v>1.88</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>6.2</v>
+        <v>3.39</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>10.41</v>
+        <v>13.65</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>18</v>
+        <v>2.59</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>34.62</v>
+        <v>19.64</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>-10.62</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3052,63 +3052,63 @@
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>25.97</v>
+        <v>13.24</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>10.73</v>
+        <v>8.58</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>8.039999999999999</v>
+        <v>2.57</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>7.2</v>
+        <v>2.09</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>10.73</v>
+        <v>8.58</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>9.33</v>
+        <v>2.57</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>27.25</v>
+        <v>13.24</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>-3.25</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>14.83</v>
+        <v>27.38</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>2.51</v>
+        <v>13.97</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>10.16</v>
+        <v>7.97</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>2.17</v>
+        <v>5.43</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
@@ -3117,45 +3117,45 @@
         <v>0</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>2.51</v>
+        <v>13.97</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>10.16</v>
+        <v>7.97</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>14.83</v>
+        <v>27.38</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>9.17</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>11.14</v>
+        <v>26.61</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1.49</v>
+        <v>11.58</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>7.23</v>
+        <v>10.68</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>2.42</v>
+        <v>4.34</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>0</v>
@@ -3164,45 +3164,45 @@
         <v>0</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>1.49</v>
+        <v>11.58</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>7.23</v>
+        <v>10.68</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>11.14</v>
+        <v>26.61</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>12.86</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>9.859999999999999</v>
+        <v>19.59</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>5.8</v>
+        <v>14.15</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.87</v>
+        <v>3.59</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>3.19</v>
+        <v>1.86</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
@@ -3211,69 +3211,69 @@
         <v>0</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>5.8</v>
+        <v>14.15</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>0.87</v>
+        <v>3.59</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>9.859999999999999</v>
+        <v>19.59</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>14.14</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>12.59</v>
+        <v>19.97</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>2.97</v>
+        <v>11.82</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>5.65</v>
+        <v>6.15</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>3.96</v>
+        <v>1.99</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>6.54</v>
+        <v>11.82</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>5.65</v>
+        <v>6.15</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>16.15</v>
+        <v>19.97</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>7.85</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3287,16 +3287,16 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>18.32</v>
+        <v>19.55</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>2.32</v>
+        <v>11.18</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>8.1</v>
+        <v>5.69</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>7.89</v>
+        <v>2.68</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
@@ -3305,22 +3305,22 @@
         <v>0</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>2.32</v>
+        <v>11.18</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>8.1</v>
+        <v>5.69</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>18.32</v>
+        <v>19.55</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>5.68</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -3334,110 +3334,110 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>16.88</v>
+        <v>0</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>4.42</v>
+        <v>1.6</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>16.88</v>
+        <v>1.6</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>7.12</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>10.67</v>
+        <v>6.93</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>3.69</v>
+        <v>0.27</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>5.22</v>
+        <v>0.05</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>1.77</v>
+        <v>6.61</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>0</v>
+        <v>19.47</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>3.69</v>
+        <v>3.14</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>5.22</v>
+        <v>19.52</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>10.67</v>
+        <v>29.27</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>13.33</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>18.95</v>
+        <v>11.96</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>9.460000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>1.33</v>
+        <v>5.77</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>8.16</v>
+        <v>2.98</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>0</v>
@@ -3446,45 +3446,45 @@
         <v>0</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>9.460000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>1.33</v>
+        <v>5.77</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>18.95</v>
+        <v>11.96</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>5.05</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>4.92</v>
+        <v>13.64</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.78</v>
+        <v>16.08</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>2.29</v>
+        <v>3.28</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
@@ -3493,27 +3493,27 @@
         <v>0</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>4.92</v>
+        <v>13.64</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>0.78</v>
+        <v>16.08</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>16</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3522,16 +3522,16 @@
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>13.59</v>
+        <v>23.92</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>6.12</v>
+        <v>5.86</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>3.33</v>
+        <v>15.77</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>4.14</v>
+        <v>2.29</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0</v>
@@ -3540,27 +3540,27 @@
         <v>0</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>6.12</v>
+        <v>5.86</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>3.33</v>
+        <v>15.77</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>13.59</v>
+        <v>23.92</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>10.41</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>15.25</v>
+        <v>29.58</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>7.12</v>
+        <v>7.75</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>2.37</v>
+        <v>18.38</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>5.76</v>
+        <v>3.45</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>0</v>
@@ -3587,74 +3587,74 @@
         <v>0</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>7.12</v>
+        <v>7.75</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>2.37</v>
+        <v>18.38</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>15.25</v>
+        <v>29.58</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>8.75</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>9.32</v>
+        <v>8.92</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>5.97</v>
+        <v>3.05</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>1.59</v>
+        <v>3.87</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>5.97</v>
+        <v>3.05</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>1.59</v>
+        <v>3.89</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>9.32</v>
+        <v>8.94</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>14.68</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -3663,16 +3663,16 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>31.9</v>
+        <v>28.68</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>11.83</v>
+        <v>14.51</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>18.05</v>
+        <v>6.36</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>2.02</v>
+        <v>7.82</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
@@ -3681,45 +3681,45 @@
         <v>0</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>11.83</v>
+        <v>14.51</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>18.05</v>
+        <v>6.36</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>31.9</v>
+        <v>28.68</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>-7.9</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>23.2</v>
+        <v>7.27</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>11.41</v>
+        <v>1.33</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>6.89</v>
+        <v>4.07</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>4.89</v>
+        <v>1.86</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>0</v>
@@ -3728,45 +3728,45 @@
         <v>0</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>11.41</v>
+        <v>1.33</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>6.89</v>
+        <v>4.07</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>23.2</v>
+        <v>7.27</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.8</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>18</v>
+        <v>18.89</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>11.38</v>
+        <v>3.62</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>3.46</v>
+        <v>13.17</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>3.17</v>
+        <v>2.1</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>0</v>
@@ -3775,27 +3775,27 @@
         <v>0</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>11.38</v>
+        <v>3.62</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>3.46</v>
+        <v>13.17</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>18</v>
+        <v>18.89</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>6</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>26.5</v>
+        <v>27.06</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>7.56</v>
+        <v>19.86</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>17.06</v>
+        <v>4.79</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0</v>
@@ -3822,67 +3822,1195 @@
         <v>0</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>7.56</v>
+        <v>19.86</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>17.06</v>
+        <v>4.79</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>26.5</v>
+        <v>27.06</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-2.5</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="M74" s="6" t="n">
+        <v>8.880000000000001</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="L76" s="6" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="M76" s="6" t="n">
+        <v>8.18</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="L78" s="6" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="M78" s="6" t="n">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="L80" s="6" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M80" s="6" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
           <t>LCB</t>
         </is>
       </c>
-      <c r="D74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M74" s="6" t="n">
-        <v>15.4</v>
+      <c r="D81" s="5" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>-10.31</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="L82" s="6" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>12.01</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L84" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M84" s="6" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>-5.58</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="L86" s="6" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="M86" s="6" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>13.35</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="L88" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M88" s="6" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>16.44</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="L90" s="6" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="M90" s="6" t="n">
+        <v>-4.13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>-6.38</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="L92" s="6" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="M92" s="6" t="n">
+        <v>-6.88</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K94" s="6" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="L94" s="6" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>13.63</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>15.16</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K96" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L96" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M96" s="6" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>21.48</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K98" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L98" s="6" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="M98" s="6" t="n">
+        <v>19.26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M74"/>
+  <autoFilter ref="A4:M98"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:09</t>
+          <t>2026-05-26 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:16</t>
+          <t>2026-05-26 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Daily_Time_24h_Check" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:20</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -4697,13 +4697,13 @@
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>30.88</v>
+        <v>36.66</v>
       </c>
       <c r="E92" s="6" t="n">
         <v>14.36</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>12.05</v>
+        <v>17.83</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>4.47</v>
@@ -4718,13 +4718,13 @@
         <v>14.36</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>12.05</v>
+        <v>17.83</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>30.88</v>
+        <v>36.66</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>-6.88</v>
+        <v>-12.66</v>
       </c>
     </row>
     <row r="93">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -4885,16 +4885,16 @@
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>4.9</v>
+        <v>21.15</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>2.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0.47</v>
+        <v>11.19</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>0</v>
@@ -4903,16 +4903,16 @@
         <v>0</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>2.56</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>0.47</v>
+        <v>11.19</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>4.9</v>
+        <v>21.15</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>19.1</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="97">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -4932,34 +4932,34 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>0</v>
+        <v>17.76</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>10.02</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>2.52</v>
+        <v>10.02</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>2.52</v>
+        <v>17.76</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>21.48</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="98">
@@ -4970,47 +4970,1222 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K98" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L98" s="6" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="M98" s="6" t="n">
+        <v>10.57</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>-14.11</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
           <t>72-1217</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>LCB</t>
         </is>
       </c>
-      <c r="D98" s="6" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E98" s="6" t="n">
+      <c r="D100" s="6" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E100" s="6" t="n">
         <v>2.97</v>
       </c>
-      <c r="F98" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G98" s="6" t="n">
+      <c r="F100" s="6" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="G100" s="6" t="n">
         <v>1.74</v>
       </c>
-      <c r="H98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="6" t="n">
+      <c r="H100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="6" t="n">
         <v>2.97</v>
       </c>
-      <c r="K98" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L98" s="6" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="M98" s="6" t="n">
-        <v>19.26</v>
+      <c r="K100" s="6" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="L100" s="6" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="M100" s="6" t="n">
+        <v>-8.1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>-7.74</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="6" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K102" s="6" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="L102" s="6" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="M102" s="6" t="n">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="M103" s="5" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="K104" s="6" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="L104" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M104" s="6" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>71-5041</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>20.85</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K106" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L106" s="6" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="M106" s="6" t="n">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="M107" s="5" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K108" s="6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="L108" s="6" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="M108" s="6" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="M109" s="5" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="6" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="K110" s="6" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="L110" s="6" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="M110" s="6" t="n">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K112" s="6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L112" s="6" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="M112" s="6" t="n">
+        <v>17.28</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>-10.37</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K114" s="6" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="L114" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M114" s="6" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="M115" s="5" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K116" s="6" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="L116" s="6" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="M116" s="6" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M117" s="5" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="K118" s="6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L118" s="6" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="M118" s="6" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M119" s="5" t="n">
+        <v>13.73</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G120" s="6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="K120" s="6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="L120" s="6" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="M120" s="6" t="n">
+        <v>14.21</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="M121" s="5" t="n">
+        <v>10.89</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="6" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M122" s="6" t="n">
+        <v>23.39</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>14.88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M98"/>
+  <autoFilter ref="A4:M123"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Daily_Time_24h_Check" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>
@@ -641,48 +641,48 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>23.21</v>
+        <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>19.9</v>
+        <v>0</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1.61</v>
+        <v>3.5</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>19.9</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>23.21</v>
+        <v>13.04</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.79</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="7">
@@ -693,101 +693,101 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>12.24</v>
+        <v>23.21</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>7.63</v>
+        <v>1.61</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2.16</v>
+        <v>19.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>9.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>11.13</v>
+        <v>1.61</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>11.7</v>
+        <v>19.9</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>25.28</v>
+        <v>23.21</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>-1.28</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>26.68</v>
+        <v>12.24</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>12.58</v>
+        <v>7.63</v>
       </c>
       <c r="F8" s="6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>12.24</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>26.68</v>
-      </c>
       <c r="M8" s="6" t="n">
-        <v>-2.68</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -796,40 +796,40 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>37.14</v>
+        <v>26.68</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>34.14</v>
+        <v>12.58</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.74</v>
+        <v>12.24</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>34.14</v>
+        <v>17.93</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.74</v>
+        <v>12.24</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>37.14</v>
+        <v>32.03</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>-13.14</v>
+        <v>-8.029999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -876,59 +876,59 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>14.58</v>
+        <v>7.85</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>6.09</v>
+        <v>5.22</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>6.86</v>
+        <v>0.82</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>11.44</v>
+        <v>5.22</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>6.86</v>
+        <v>0.82</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>19.93</v>
+        <v>7.85</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>4.07</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>22.68</v>
+        <v>14.58</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>18.54</v>
+        <v>6.09</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3.21</v>
+        <v>1.63</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0</v>
@@ -955,16 +955,16 @@
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>18.54</v>
+        <v>6.09</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>22.68</v>
+        <v>14.58</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>1.32</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="13">
@@ -975,25 +975,25 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>7.85</v>
+        <v>37.14</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>5.22</v>
+        <v>34.14</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
@@ -1002,16 +1002,16 @@
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>5.22</v>
+        <v>34.14</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>7.85</v>
+        <v>37.14</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>16.15</v>
+        <v>-13.14</v>
       </c>
     </row>
     <row r="14">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>22.03</v>
+        <v>22.68</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7.02</v>
+        <v>18.54</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>11.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3.49</v>
+        <v>3.21</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
@@ -1049,27 +1049,27 @@
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>7.02</v>
+        <v>18.54</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>11.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>22.03</v>
+        <v>22.68</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>25.02</v>
+        <v>22.03</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>14.52</v>
+        <v>7.02</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8.73</v>
+        <v>11.51</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.77</v>
+        <v>3.49</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
@@ -1096,27 +1096,27 @@
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>14.52</v>
+        <v>7.02</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>8.73</v>
+        <v>11.51</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>25.02</v>
+        <v>22.03</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>-1.02</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1125,16 +1125,16 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>24.32</v>
+        <v>35.65</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>13.41</v>
+        <v>22.42</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>7.22</v>
+        <v>9.83</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
@@ -1143,16 +1143,16 @@
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>13.41</v>
+        <v>22.42</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>7.22</v>
+        <v>9.83</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>24.32</v>
+        <v>35.65</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-0.32</v>
+        <v>-11.65</v>
       </c>
     </row>
     <row r="17">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10.63</v>
+        <v>32.19</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>7.9</v>
+        <v>18.19</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1.1</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1.62</v>
+        <v>5.62</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
@@ -1190,27 +1190,27 @@
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>7.9</v>
+        <v>18.19</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1.1</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>10.63</v>
+        <v>32.19</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>13.37</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1219,16 +1219,16 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>7.88</v>
+        <v>15.89</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>4.78</v>
+        <v>8.24</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1.17</v>
+        <v>3.12</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.93</v>
+        <v>4.53</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
@@ -1237,16 +1237,16 @@
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>4.78</v>
+        <v>8.24</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1.17</v>
+        <v>3.12</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>7.88</v>
+        <v>15.89</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>16.12</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>15.89</v>
+        <v>14.37</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>8.24</v>
+        <v>5.73</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>4.53</v>
+        <v>4.94</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -1284,45 +1284,45 @@
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>8.24</v>
+        <v>5.73</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>15.89</v>
+        <v>14.37</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>8.109999999999999</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14.37</v>
+        <v>19.22</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5.73</v>
+        <v>7.04</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>3.7</v>
+        <v>10.08</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4.94</v>
+        <v>2.11</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
@@ -1331,16 +1331,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>5.73</v>
+        <v>7.04</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>3.7</v>
+        <v>10.08</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>14.37</v>
+        <v>19.22</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>9.630000000000001</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="21">
@@ -1351,25 +1351,25 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>30.03</v>
+        <v>14.11</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>8.9</v>
+        <v>7.61</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>18.47</v>
+        <v>4.73</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>2.67</v>
+        <v>1.77</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
@@ -1378,16 +1378,16 @@
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>8.9</v>
+        <v>7.61</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>18.47</v>
+        <v>4.73</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>30.03</v>
+        <v>14.11</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>-6.03</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1398,25 +1398,25 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>19.22</v>
+        <v>18.8</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7.04</v>
+        <v>7.61</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>10.08</v>
+        <v>8.57</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -1425,45 +1425,45 @@
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>7.04</v>
+        <v>7.61</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>10.08</v>
+        <v>8.57</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>19.22</v>
+        <v>18.8</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>4.78</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>27.33</v>
+        <v>30.03</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>13.55</v>
+        <v>8.9</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>10.43</v>
+        <v>18.47</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3.36</v>
+        <v>2.67</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -1472,45 +1472,45 @@
         <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>13.55</v>
+        <v>8.9</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>10.43</v>
+        <v>18.47</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>27.33</v>
+        <v>30.03</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-3.33</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18.8</v>
+        <v>15</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7.61</v>
+        <v>5.78</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>8.57</v>
+        <v>6.55</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
@@ -1519,16 +1519,16 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7.61</v>
+        <v>5.78</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>8.57</v>
+        <v>6.55</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>18.8</v>
+        <v>15</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -1539,25 +1539,25 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>20.51</v>
+        <v>22.04</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>9.380000000000001</v>
+        <v>11.33</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>5.55</v>
+        <v>6.72</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>5.58</v>
+        <v>4</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0</v>
@@ -1566,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>9.380000000000001</v>
+        <v>11.33</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>5.55</v>
+        <v>6.72</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>20.51</v>
+        <v>22.04</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>3.49</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="26">
@@ -1586,25 +1586,25 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>15</v>
+        <v>7.29</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5.78</v>
+        <v>2.63</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>6.55</v>
+        <v>2.38</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
@@ -1613,45 +1613,45 @@
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>5.78</v>
+        <v>2.63</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>6.55</v>
+        <v>2.38</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>15</v>
+        <v>7.29</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>9</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>28.99</v>
+        <v>27.75</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>11.22</v>
+        <v>14.11</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>13.3</v>
+        <v>6.33</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>4.47</v>
+        <v>7.31</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
@@ -1660,45 +1660,45 @@
         <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>11.22</v>
+        <v>14.11</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>13.3</v>
+        <v>6.33</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>28.99</v>
+        <v>27.75</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>-4.99</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>23.27</v>
+        <v>19.15</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>12.14</v>
+        <v>14.59</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>6.63</v>
+        <v>2.46</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>4.49</v>
+        <v>2.09</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
@@ -1707,16 +1707,16 @@
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>12.14</v>
+        <v>14.59</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>6.63</v>
+        <v>2.46</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>23.27</v>
+        <v>19.15</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>0.73</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="29">
@@ -1727,25 +1727,25 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>7.24</v>
+        <v>24.51</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4.73</v>
+        <v>7.61</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.78</v>
+        <v>12.94</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.73</v>
+        <v>3.96</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
@@ -1754,16 +1754,16 @@
         <v>0</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>4.73</v>
+        <v>7.61</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.78</v>
+        <v>12.94</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>7.24</v>
+        <v>24.51</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>16.76</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="30">
@@ -1774,25 +1774,25 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>19.15</v>
+        <v>26.64</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>14.59</v>
+        <v>16.99</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2.09</v>
+        <v>4.16</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
@@ -1801,45 +1801,45 @@
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>14.59</v>
+        <v>16.99</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>2.46</v>
+        <v>5.5</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>19.15</v>
+        <v>26.64</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>4.85</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>4.35</v>
+        <v>13.67</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1.79</v>
+        <v>10.38</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.66</v>
+        <v>1.29</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
@@ -1848,45 +1848,45 @@
         <v>0</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1.79</v>
+        <v>10.38</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.66</v>
+        <v>1.29</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>4.35</v>
+        <v>13.67</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>19.65</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>10.66</v>
+        <v>16.65</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>7.47</v>
+        <v>12.52</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.24</v>
+        <v>2.07</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0</v>
@@ -1895,16 +1895,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>7.47</v>
+        <v>12.52</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1.24</v>
+        <v>2.07</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>10.66</v>
+        <v>16.65</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>13.34</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="33">
@@ -1915,54 +1915,54 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>13.67</v>
+        <v>19.38</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>10.38</v>
+        <v>15.37</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>10.38</v>
+        <v>15.89</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>13.67</v>
+        <v>19.9</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>10.33</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>27.88</v>
+        <v>6.38</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>18.42</v>
+        <v>2.04</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>5.43</v>
+        <v>2.32</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>4.02</v>
+        <v>2.02</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0</v>
@@ -1989,63 +1989,63 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>18.42</v>
+        <v>2.04</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>5.43</v>
+        <v>2.32</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>27.88</v>
+        <v>6.38</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>-3.88</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>19.38</v>
+        <v>17.85</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>15.37</v>
+        <v>8.26</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1.41</v>
+        <v>5.43</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2.59</v>
+        <v>4.17</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>15.89</v>
+        <v>8.26</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>1.41</v>
+        <v>5.43</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>19.9</v>
+        <v>17.85</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>4.1</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="36">
@@ -2056,43 +2056,43 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8683</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>23.79</v>
+        <v>0</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>13.35</v>
+        <v>0</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>13.35</v>
+        <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>4.51</v>
+        <v>1.49</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>23.79</v>
+        <v>1.49</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>0.21</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="37">
@@ -2103,25 +2103,25 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>27.17</v>
+        <v>16.45</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>19.94</v>
+        <v>4.25</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>3.18</v>
+        <v>10.67</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>4.05</v>
+        <v>1.53</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0</v>
@@ -2130,92 +2130,92 @@
         <v>0</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>19.94</v>
+        <v>4.25</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>3.18</v>
+        <v>10.67</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>27.17</v>
+        <v>16.45</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>-3.17</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>71-8683</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0</v>
+        <v>13.83</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0</v>
+        <v>13.83</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1.49</v>
+        <v>4.16</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>1.49</v>
+        <v>23.9</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>22.51</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>29.48</v>
+        <v>29.74</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>13.75</v>
+        <v>21.91</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>12.64</v>
+        <v>4.07</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>3.09</v>
+        <v>3.76</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0</v>
@@ -2224,16 +2224,16 @@
         <v>0</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>13.75</v>
+        <v>21.91</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>12.64</v>
+        <v>4.07</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>29.48</v>
+        <v>29.74</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-5.48</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="40">
@@ -2244,25 +2244,25 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>6.48</v>
+        <v>22.21</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>2.52</v>
+        <v>14.16</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1.96</v>
+        <v>4.87</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>2</v>
+        <v>3.18</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0</v>
@@ -2271,27 +2271,27 @@
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>2.52</v>
+        <v>14.16</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>1.96</v>
+        <v>4.87</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>6.48</v>
+        <v>22.21</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>17.52</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2300,16 +2300,16 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0</v>
@@ -2318,63 +2318,63 @@
         <v>0</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>14.8</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>20.76</v>
+        <v>0</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>5.48</v>
+        <v>0.37</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>20.76</v>
+        <v>0.37</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>3.24</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="43">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2394,16 +2394,16 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>29.13</v>
+        <v>9.66</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>12.26</v>
+        <v>1.85</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>0</v>
@@ -2412,16 +2412,16 @@
         <v>0</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>29.13</v>
+        <v>9.66</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>-5.13</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="44">
@@ -2432,54 +2432,54 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0</v>
+        <v>19.71</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0</v>
+        <v>12.69</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0</v>
+        <v>12.69</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.37</v>
+        <v>3.78</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.37</v>
+        <v>19.71</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>23.63</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2488,16 +2488,16 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>22.59</v>
+        <v>20.16</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>12.43</v>
+        <v>5.72</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>6.4</v>
+        <v>4.45</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>3.77</v>
+        <v>10</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>0</v>
@@ -2506,45 +2506,45 @@
         <v>0</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>12.43</v>
+        <v>5.72</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>6.4</v>
+        <v>4.45</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>22.59</v>
+        <v>20.16</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>1.41</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>20.29</v>
+        <v>26.48</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>10.52</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>6.05</v>
+        <v>13.45</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
@@ -2553,16 +2553,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>10.52</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>6.05</v>
+        <v>13.45</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>20.29</v>
+        <v>26.48</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>3.71</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="47">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>21.67</v>
+        <v>12.93</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>6.68</v>
+        <v>6.21</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>13.43</v>
+        <v>4.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0</v>
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>6.68</v>
+        <v>6.21</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>13.43</v>
+        <v>4.8</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>21.67</v>
+        <v>12.93</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>2.33</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="48">
@@ -2620,25 +2620,25 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>26.48</v>
+        <v>22.85</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>13.39</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>13.45</v>
+        <v>5.66</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0</v>
@@ -2647,27 +2647,27 @@
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>13.39</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>13.45</v>
+        <v>5.66</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>26.48</v>
+        <v>22.85</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>-2.48</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -2676,16 +2676,16 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>24.81</v>
+        <v>21.67</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2.76</v>
+        <v>6.68</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>19.43</v>
+        <v>13.43</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="H49" s="5" t="n">
         <v>0</v>
@@ -2694,45 +2694,45 @@
         <v>0</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>2.76</v>
+        <v>6.68</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>19.43</v>
+        <v>13.43</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>24.81</v>
+        <v>21.67</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>10.7</v>
+        <v>15.1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>7.97</v>
+        <v>4.35</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.82</v>
+        <v>6.98</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>1.91</v>
+        <v>3.77</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
@@ -2741,16 +2741,16 @@
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>7.97</v>
+        <v>4.35</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>0.82</v>
+        <v>6.98</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>10.7</v>
+        <v>15.1</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>13.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="51">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -2770,16 +2770,16 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>15.1</v>
+        <v>24.81</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>4.35</v>
+        <v>2.76</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>6.98</v>
+        <v>19.43</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>3.77</v>
+        <v>2.62</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0</v>
@@ -2788,16 +2788,16 @@
         <v>0</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>4.35</v>
+        <v>2.76</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>6.98</v>
+        <v>19.43</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>15.1</v>
+        <v>24.81</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>8.9</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2817,16 +2817,16 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>29.14</v>
+        <v>13.83</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>22.27</v>
+        <v>10.75</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>3.37</v>
+        <v>1.23</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3.51</v>
+        <v>1.86</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
@@ -2835,16 +2835,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>22.27</v>
+        <v>10.75</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>3.37</v>
+        <v>1.23</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>29.14</v>
+        <v>13.83</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-5.14</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="53">
@@ -2911,16 +2911,16 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>12.76</v>
+        <v>28.07</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>7.56</v>
+        <v>19.07</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>2.84</v>
+        <v>4.98</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>2.37</v>
+        <v>4.01</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>7.56</v>
+        <v>19.07</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>2.84</v>
+        <v>4.98</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>12.76</v>
+        <v>28.07</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>11.24</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="55">
@@ -3005,16 +3005,16 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>18.92</v>
+        <v>6.74</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>13.65</v>
+        <v>4.28</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>1.88</v>
+        <v>0.64</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>3.39</v>
+        <v>1.82</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
@@ -3023,16 +3023,16 @@
         <v>0.72</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>13.65</v>
+        <v>4.28</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>2.59</v>
+        <v>1.36</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>19.64</v>
+        <v>7.46</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>4.36</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="57">
@@ -3043,25 +3043,25 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>13.24</v>
+        <v>8.98</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>8.58</v>
+        <v>6.37</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>2.57</v>
+        <v>1.05</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2.09</v>
+        <v>1.56</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>0</v>
@@ -3070,45 +3070,45 @@
         <v>0</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>8.58</v>
+        <v>6.37</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>2.57</v>
+        <v>1.05</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>13.24</v>
+        <v>8.98</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>10.76</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>27.38</v>
+        <v>11.17</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>13.97</v>
+        <v>3.44</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>7.97</v>
+        <v>5.1</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>5.43</v>
+        <v>2.63</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
@@ -3117,16 +3117,16 @@
         <v>0</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>13.97</v>
+        <v>3.44</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>7.97</v>
+        <v>5.1</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>27.38</v>
+        <v>11.17</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>-3.38</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="59">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3146,16 +3146,16 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>26.61</v>
+        <v>31.78</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>11.58</v>
+        <v>23.53</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>10.68</v>
+        <v>4.82</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>4.34</v>
+        <v>3.43</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>0</v>
@@ -3164,16 +3164,16 @@
         <v>0</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>11.58</v>
+        <v>23.53</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>10.68</v>
+        <v>4.82</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>26.61</v>
+        <v>31.78</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>-2.61</v>
+        <v>-7.78</v>
       </c>
     </row>
     <row r="60">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -3193,16 +3193,16 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>19.59</v>
+        <v>13.24</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>14.15</v>
+        <v>8.58</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>3.59</v>
+        <v>2.57</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
@@ -3211,16 +3211,16 @@
         <v>0</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>14.15</v>
+        <v>8.58</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>3.59</v>
+        <v>2.57</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>19.59</v>
+        <v>13.24</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>4.41</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="61">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>19.97</v>
+        <v>18.4</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>11.82</v>
+        <v>7.6</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>6.15</v>
+        <v>6.93</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1.99</v>
+        <v>3.87</v>
       </c>
       <c r="H61" s="5" t="n">
         <v>0</v>
@@ -3258,63 +3258,63 @@
         <v>0</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>11.82</v>
+        <v>7.6</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>6.15</v>
+        <v>6.93</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>19.97</v>
+        <v>18.4</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>4.03</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>19.55</v>
+        <v>0</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>11.18</v>
+        <v>0</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>11.18</v>
+        <v>0</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>5.69</v>
+        <v>1.6</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>19.55</v>
+        <v>1.6</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>4.45</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="63">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3334,34 +3334,34 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>1.6</v>
+        <v>19.47</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>1.6</v>
+        <v>19.52</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>1.6</v>
+        <v>29.27</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>22.4</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="64">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -3381,34 +3381,34 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>6.93</v>
+        <v>27.41</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>0.27</v>
+        <v>11.36</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.05</v>
+        <v>11.35</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>6.61</v>
+        <v>4.7</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>19.47</v>
+        <v>0</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>3.14</v>
+        <v>11.36</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>19.52</v>
+        <v>11.35</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>29.27</v>
+        <v>27.41</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>-5.27</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="65">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>11.96</v>
+        <v>13.31</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3.21</v>
+        <v>7.37</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>5.77</v>
+        <v>4.29</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>2.98</v>
+        <v>1.65</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>0</v>
@@ -3446,16 +3446,16 @@
         <v>0</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>3.21</v>
+        <v>7.37</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>5.77</v>
+        <v>4.29</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>11.96</v>
+        <v>13.31</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>12.04</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="66">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -3475,16 +3475,16 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>33</v>
+        <v>19.97</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>13.64</v>
+        <v>11.82</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>16.08</v>
+        <v>6.15</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>3.28</v>
+        <v>1.99</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
@@ -3493,16 +3493,16 @@
         <v>0</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>13.64</v>
+        <v>11.82</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>16.08</v>
+        <v>6.15</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>33</v>
+        <v>19.97</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>-9</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="67">
@@ -3513,25 +3513,25 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>23.92</v>
+        <v>26.52</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5.86</v>
+        <v>13.27</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>15.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2.29</v>
+        <v>4.47</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0</v>
@@ -3540,63 +3540,63 @@
         <v>0</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>5.86</v>
+        <v>13.27</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>15.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>23.92</v>
+        <v>26.52</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.08</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>29.58</v>
+        <v>8.92</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>7.75</v>
+        <v>3.05</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>18.38</v>
+        <v>3.87</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3.45</v>
+        <v>2</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>7.75</v>
+        <v>3.05</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>18.38</v>
+        <v>3.89</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>29.58</v>
+        <v>8.94</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>-5.58</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="69">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -3616,34 +3616,34 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>8.92</v>
+        <v>16.04</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>3.05</v>
+        <v>6.71</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>3.87</v>
+        <v>4.76</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>2</v>
+        <v>4.57</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>3.05</v>
+        <v>6.71</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>3.89</v>
+        <v>4.76</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>8.94</v>
+        <v>16.04</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>15.06</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="70">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -3663,16 +3663,16 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>28.68</v>
+        <v>26.95</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>14.51</v>
+        <v>7.6</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>6.36</v>
+        <v>15.85</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>7.82</v>
+        <v>3.5</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
@@ -3681,16 +3681,16 @@
         <v>0</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>14.51</v>
+        <v>7.6</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>6.36</v>
+        <v>15.85</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>28.68</v>
+        <v>26.95</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>-4.68</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="71">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>7.27</v>
+        <v>23.92</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1.33</v>
+        <v>5.86</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>4.07</v>
+        <v>15.77</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>0</v>
@@ -3728,16 +3728,16 @@
         <v>0</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>1.33</v>
+        <v>5.86</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>4.07</v>
+        <v>15.77</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>7.27</v>
+        <v>23.92</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>16.73</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="72">
@@ -3748,25 +3748,25 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>18.89</v>
+        <v>22.61</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>3.62</v>
+        <v>5.66</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>13.17</v>
+        <v>15.29</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>0</v>
@@ -3775,45 +3775,45 @@
         <v>0</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>3.62</v>
+        <v>5.66</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>13.17</v>
+        <v>15.29</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>18.89</v>
+        <v>22.61</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>5.11</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>27.06</v>
+        <v>15.12</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>19.86</v>
+        <v>5.1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4.79</v>
+        <v>5.37</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>2.41</v>
+        <v>4.65</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0</v>
@@ -3822,16 +3822,16 @@
         <v>0</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>19.86</v>
+        <v>5.1</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>4.79</v>
+        <v>5.37</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>27.06</v>
+        <v>15.12</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-3.06</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -3851,16 +3851,16 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>15.12</v>
+        <v>12.64</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>5.37</v>
+        <v>1.6</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>4.65</v>
+        <v>3.24</v>
       </c>
       <c r="H74" s="6" t="n">
         <v>0</v>
@@ -3869,16 +3869,16 @@
         <v>0</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>5.37</v>
+        <v>1.6</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>15.12</v>
+        <v>12.64</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>8.880000000000001</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="75">
@@ -3945,16 +3945,16 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>15.82</v>
+        <v>18.89</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>4.35</v>
+        <v>3.62</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>9.57</v>
+        <v>13.17</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H76" s="6" t="n">
         <v>0</v>
@@ -3963,45 +3963,45 @@
         <v>0</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>4.35</v>
+        <v>3.62</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>9.57</v>
+        <v>13.17</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>15.82</v>
+        <v>18.89</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>8.18</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>23.43</v>
+        <v>27.06</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>8.529999999999999</v>
+        <v>19.86</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>8.119999999999999</v>
+        <v>4.79</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>6.79</v>
+        <v>2.41</v>
       </c>
       <c r="H77" s="5" t="n">
         <v>0</v>
@@ -4010,16 +4010,16 @@
         <v>0</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>8.529999999999999</v>
+        <v>19.86</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>8.119999999999999</v>
+        <v>4.79</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>23.43</v>
+        <v>27.06</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>0.57</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="78">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -4039,34 +4039,34 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>4.13</v>
+        <v>1.89</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>3.19</v>
+        <v>2.48</v>
       </c>
       <c r="G78" s="6" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K78" s="6" t="n">
         <v>2.48</v>
       </c>
-      <c r="H78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J78" s="6" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="K78" s="6" t="n">
-        <v>3.69</v>
-      </c>
       <c r="L78" s="6" t="n">
-        <v>10.31</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>13.69</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="79">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4086,34 +4086,34 @@
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>12.64</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E79" s="5" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="K79" s="5" t="n">
         <v>3.69</v>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>9.16</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>6.64</v>
-      </c>
       <c r="L79" s="5" t="n">
-        <v>21.8</v>
+        <v>10.31</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>2.2</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="80">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -4133,34 +4133,34 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>10.8</v>
+        <v>12.64</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>4.12</v>
+        <v>3.69</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>4.32</v>
+        <v>6.64</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="I80" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>4.12</v>
+        <v>12.85</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>4.32</v>
+        <v>6.64</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>10.8</v>
+        <v>21.8</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>13.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="81">
@@ -4171,25 +4171,25 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>34.31</v>
+        <v>26.63</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>12.2</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>17.77</v>
+        <v>13.89</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>4.34</v>
+        <v>4.27</v>
       </c>
       <c r="H81" s="5" t="n">
         <v>0</v>
@@ -4198,45 +4198,45 @@
         <v>0</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>12.2</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>17.77</v>
+        <v>13.89</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>34.31</v>
+        <v>26.63</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-10.31</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>11.99</v>
+        <v>12.77</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>7.66</v>
+        <v>9.25</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="H82" s="6" t="n">
         <v>0</v>
@@ -4245,16 +4245,16 @@
         <v>0</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>7.66</v>
+        <v>9.25</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>11.99</v>
+        <v>12.77</v>
       </c>
       <c r="M82" s="6" t="n">
-        <v>12.01</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="83">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -4274,16 +4274,16 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>15.77</v>
+        <v>26.03</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>3.53</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>10.61</v>
+        <v>13.29</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1.64</v>
+        <v>4.03</v>
       </c>
       <c r="H83" s="5" t="n">
         <v>0</v>
@@ -4292,16 +4292,16 @@
         <v>0</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>3.53</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>10.61</v>
+        <v>13.29</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>15.77</v>
+        <v>26.03</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>8.23</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="84">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -4321,34 +4321,34 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>4.69</v>
+        <v>15.77</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>0.13</v>
+        <v>3.53</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>2.81</v>
+        <v>10.61</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I84" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>7.13</v>
+        <v>3.53</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>2.81</v>
+        <v>10.61</v>
       </c>
       <c r="L84" s="6" t="n">
-        <v>11.7</v>
+        <v>15.77</v>
       </c>
       <c r="M84" s="6" t="n">
-        <v>12.3</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="85">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -4368,34 +4368,34 @@
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>29.58</v>
+        <v>4.69</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>13.77</v>
+        <v>0.13</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>12.18</v>
+        <v>2.81</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>3.63</v>
+        <v>1.75</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>13.77</v>
+        <v>7.13</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>12.18</v>
+        <v>2.81</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>29.58</v>
+        <v>11.7</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>-5.58</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="86">
@@ -4406,25 +4406,25 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>17.57</v>
+        <v>14.2</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>6.6</v>
+        <v>5.16</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>9.34</v>
+        <v>7.37</v>
       </c>
       <c r="G86" s="6" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="H86" s="6" t="n">
         <v>0</v>
@@ -4433,45 +4433,45 @@
         <v>0</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>6.6</v>
+        <v>5.16</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>9.34</v>
+        <v>7.37</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>17.57</v>
+        <v>14.2</v>
       </c>
       <c r="M86" s="6" t="n">
-        <v>6.43</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>10.65</v>
+        <v>21.53</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>5.46</v>
+        <v>10.4</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>3.53</v>
+        <v>8.52</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1.66</v>
+        <v>2.61</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>0</v>
@@ -4480,16 +4480,16 @@
         <v>0</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>5.46</v>
+        <v>10.4</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>3.53</v>
+        <v>8.52</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>10.65</v>
+        <v>21.53</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>13.35</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="88">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -4509,34 +4509,34 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>19.98</v>
+        <v>10.65</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>11.59</v>
+        <v>5.46</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>4.56</v>
+        <v>3.53</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>3.84</v>
+        <v>1.66</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>11.59</v>
+        <v>5.46</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>5.68</v>
+        <v>3.53</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>21.1</v>
+        <v>10.65</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>2.9</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="89">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -4556,34 +4556,34 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>7.56</v>
+        <v>19.98</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3.95</v>
+        <v>11.59</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.89</v>
+        <v>4.56</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>2.73</v>
+        <v>3.84</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>3.95</v>
+        <v>11.59</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>0.89</v>
+        <v>5.68</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>7.56</v>
+        <v>21.1</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>16.44</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="90">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -4603,16 +4603,16 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>28.13</v>
+        <v>7.56</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>9.859999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>9.32</v>
+        <v>0.89</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>8.960000000000001</v>
+        <v>2.73</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>0</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>9.859999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>9.32</v>
+        <v>0.89</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>28.13</v>
+        <v>7.56</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>-4.13</v>
+        <v>16.44</v>
       </c>
     </row>
     <row r="91">
@@ -4641,25 +4641,25 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>30.38</v>
+        <v>22.16</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>8.57</v>
+        <v>13.02</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>8.74</v>
+        <v>5.4</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>13.07</v>
+        <v>3.74</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>0</v>
@@ -4668,45 +4668,45 @@
         <v>0</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>8.57</v>
+        <v>13.02</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>8.74</v>
+        <v>5.4</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>30.38</v>
+        <v>22.16</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>-6.38</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>36.66</v>
+        <v>25.17</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>14.36</v>
+        <v>11.43</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>17.83</v>
+        <v>10.48</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>4.47</v>
+        <v>3.26</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>0</v>
@@ -4715,16 +4715,16 @@
         <v>0</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>14.36</v>
+        <v>11.43</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>17.83</v>
+        <v>10.48</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>36.66</v>
+        <v>25.17</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>-12.66</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="93">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -4744,16 +4744,16 @@
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>13.4</v>
+        <v>13.45</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1.31</v>
+        <v>3.04</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>8.49</v>
+        <v>7.73</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>0</v>
@@ -4762,16 +4762,16 @@
         <v>0</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>1.31</v>
+        <v>3.04</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>8.49</v>
+        <v>7.73</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>13.4</v>
+        <v>13.45</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>10.6</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="94">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -4791,16 +4791,16 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>10.37</v>
+        <v>13.4</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>6.57</v>
+        <v>8.49</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="H94" s="6" t="n">
         <v>0</v>
@@ -4809,16 +4809,16 @@
         <v>0</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>1.89</v>
+        <v>1.31</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>6.57</v>
+        <v>8.49</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>10.37</v>
+        <v>13.4</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>13.63</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="95">
@@ -4829,25 +4829,25 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>8.84</v>
+        <v>21.35</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1.34</v>
+        <v>5.45</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>5.87</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1.63</v>
+        <v>7.18</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>0</v>
@@ -4856,45 +4856,45 @@
         <v>0</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>1.34</v>
+        <v>5.45</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>5.87</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>8.84</v>
+        <v>21.35</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>15.16</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>21.15</v>
+        <v>31.63</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>5.08</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>11.19</v>
+        <v>13.47</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>1.66</v>
+        <v>13.07</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>0</v>
@@ -4903,16 +4903,16 @@
         <v>0</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>5.08</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>11.19</v>
+        <v>13.47</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>21.15</v>
+        <v>31.63</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>2.85</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="97">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -4932,16 +4932,16 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>17.76</v>
+        <v>23.21</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>10.02</v>
+        <v>11.32</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>5.61</v>
+        <v>10.1</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>0</v>
@@ -4950,16 +4950,16 @@
         <v>0</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>10.02</v>
+        <v>11.32</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>5.61</v>
+        <v>10.1</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>17.76</v>
+        <v>23.21</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>6.24</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="98">
@@ -5026,16 +5026,16 @@
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>38.11</v>
+        <v>10.37</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>32.02</v>
+        <v>6.57</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0</v>
@@ -5044,45 +5044,45 @@
         <v>0</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>32.02</v>
+        <v>6.57</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>38.11</v>
+        <v>10.37</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>-14.11</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>32.1</v>
+        <v>21.15</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>2.97</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>27.39</v>
+        <v>11.19</v>
       </c>
       <c r="G100" s="6" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="H100" s="6" t="n">
         <v>0</v>
@@ -5091,16 +5091,16 @@
         <v>0</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>2.97</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>27.39</v>
+        <v>11.19</v>
       </c>
       <c r="L100" s="6" t="n">
-        <v>32.1</v>
+        <v>21.15</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>-8.1</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="101">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>31.74</v>
+        <v>17.76</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>19.06</v>
+        <v>10.02</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>10.8</v>
+        <v>5.61</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="H101" s="5" t="n">
         <v>0</v>
@@ -5138,16 +5138,16 @@
         <v>0</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>19.06</v>
+        <v>10.02</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>10.8</v>
+        <v>5.61</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>31.74</v>
+        <v>17.76</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>-7.74</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="102">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -5167,16 +5167,16 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>15.17</v>
+        <v>38.11</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>3.81</v>
+        <v>4.4</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>9.43</v>
+        <v>32.02</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>0</v>
@@ -5185,16 +5185,16 @@
         <v>0</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>3.81</v>
+        <v>4.4</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>9.43</v>
+        <v>32.02</v>
       </c>
       <c r="L102" s="6" t="n">
-        <v>15.17</v>
+        <v>38.11</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>8.83</v>
+        <v>-14.11</v>
       </c>
     </row>
     <row r="103">
@@ -5205,25 +5205,25 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>14.86</v>
+        <v>32.1</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>4.66</v>
+        <v>2.97</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>7.99</v>
+        <v>27.39</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>2.21</v>
+        <v>1.74</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>0</v>
@@ -5232,63 +5232,63 @@
         <v>0</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>4.66</v>
+        <v>2.97</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>7.99</v>
+        <v>27.39</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>14.86</v>
+        <v>32.1</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>9.140000000000001</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>11.61</v>
+        <v>0</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>11.61</v>
+        <v>3.15</v>
       </c>
       <c r="L104" s="6" t="n">
-        <v>16.5</v>
+        <v>3.15</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>7.5</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="105">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -5308,34 +5308,34 @@
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>0</v>
+        <v>31.74</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>19.06</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="H105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>0</v>
+        <v>19.06</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>3.15</v>
+        <v>10.8</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>3.15</v>
+        <v>31.74</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>20.85</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="106">
@@ -5355,16 +5355,16 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>13.55</v>
+        <v>19.5</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>3.1</v>
+        <v>5.69</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>7.3</v>
+        <v>10.31</v>
       </c>
       <c r="G106" s="6" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="H106" s="6" t="n">
         <v>0</v>
@@ -5373,16 +5373,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>3.1</v>
+        <v>5.69</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>7.3</v>
+        <v>10.31</v>
       </c>
       <c r="L106" s="6" t="n">
-        <v>13.55</v>
+        <v>19.5</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>10.45</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="107">
@@ -5402,16 +5402,16 @@
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>20.99</v>
+        <v>21.49</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>9.91</v>
+        <v>7.63</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>6.61</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>4.48</v>
+        <v>4.57</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
@@ -5420,16 +5420,16 @@
         <v>0</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>9.91</v>
+        <v>7.63</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>6.61</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>20.99</v>
+        <v>21.49</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>3.01</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="108">
@@ -5496,16 +5496,16 @@
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>17.35</v>
+        <v>16.5</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>7.33</v>
+        <v>3.28</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>11.61</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>0</v>
@@ -5514,16 +5514,16 @@
         <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>7.33</v>
+        <v>3.28</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>11.61</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>17.35</v>
+        <v>16.5</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="110">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>22.21</v>
+        <v>18.22</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>8.92</v>
+        <v>7.66</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>2.42</v>
+        <v>7.12</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>10.87</v>
+        <v>3.44</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>0</v>
@@ -5608,16 +5608,16 @@
         <v>0</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>8.92</v>
+        <v>7.66</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>2.42</v>
+        <v>7.12</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>22.21</v>
+        <v>18.22</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>1.79</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="112">
@@ -5637,16 +5637,16 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>6.72</v>
+        <v>21.08</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>1.56</v>
+        <v>8.5</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>2.7</v>
+        <v>8.01</v>
       </c>
       <c r="G112" s="6" t="n">
-        <v>2.46</v>
+        <v>4.57</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>0</v>
@@ -5655,16 +5655,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>1.56</v>
+        <v>8.5</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>2.7</v>
+        <v>8.01</v>
       </c>
       <c r="L112" s="6" t="n">
-        <v>6.72</v>
+        <v>21.08</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>17.28</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="113">
@@ -5684,16 +5684,16 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>34.37</v>
+        <v>19.32</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>19.72</v>
+        <v>12.75</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>7.79</v>
+        <v>2.68</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>6.86</v>
+        <v>3.9</v>
       </c>
       <c r="H113" s="5" t="n">
         <v>0</v>
@@ -5702,16 +5702,16 @@
         <v>0</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>19.72</v>
+        <v>12.75</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>7.79</v>
+        <v>2.68</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>34.37</v>
+        <v>19.32</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>-10.37</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="114">
@@ -5731,16 +5731,16 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>21.9</v>
+        <v>17.35</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>3.7</v>
+        <v>7.33</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>16.49</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G114" s="6" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="H114" s="6" t="n">
         <v>0</v>
@@ -5749,16 +5749,16 @@
         <v>0</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>3.7</v>
+        <v>7.33</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>16.49</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L114" s="6" t="n">
-        <v>21.9</v>
+        <v>17.35</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>2.1</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="115">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>22.44</v>
+        <v>11.92</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>11.02</v>
+        <v>3.66</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>7.21</v>
+        <v>6.14</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>4.21</v>
+        <v>2.13</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
@@ -5796,16 +5796,16 @@
         <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>11.02</v>
+        <v>3.66</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>7.21</v>
+        <v>6.14</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>22.44</v>
+        <v>11.92</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>1.56</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="116">
@@ -5825,16 +5825,16 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>20.28</v>
+        <v>23.52</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>7.9</v>
+        <v>4.75</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>8.73</v>
+        <v>7.66</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>3.64</v>
+        <v>11.11</v>
       </c>
       <c r="H116" s="6" t="n">
         <v>0</v>
@@ -5843,16 +5843,16 @@
         <v>0</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>7.9</v>
+        <v>4.75</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>8.73</v>
+        <v>7.66</v>
       </c>
       <c r="L116" s="6" t="n">
-        <v>20.28</v>
+        <v>23.52</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>3.72</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="117">
@@ -5919,16 +5919,16 @@
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>15.44</v>
+        <v>15.05</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>12.56</v>
+        <v>6.97</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1.08</v>
+        <v>5.11</v>
       </c>
       <c r="G118" s="6" t="n">
-        <v>1.79</v>
+        <v>2.97</v>
       </c>
       <c r="H118" s="6" t="n">
         <v>0</v>
@@ -5937,16 +5937,16 @@
         <v>0</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>12.56</v>
+        <v>6.97</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>1.08</v>
+        <v>5.11</v>
       </c>
       <c r="L118" s="6" t="n">
-        <v>15.44</v>
+        <v>15.05</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>8.56</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -5966,16 +5966,16 @@
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>10.27</v>
+        <v>32.17</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>6.29</v>
+        <v>9.98</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>2.26</v>
+        <v>18.74</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>1.73</v>
+        <v>3.44</v>
       </c>
       <c r="H119" s="5" t="n">
         <v>0</v>
@@ -5984,16 +5984,16 @@
         <v>0</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>6.29</v>
+        <v>9.98</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>2.26</v>
+        <v>18.74</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>10.27</v>
+        <v>32.17</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>13.73</v>
+        <v>-8.17</v>
       </c>
     </row>
     <row r="120">
@@ -6013,16 +6013,16 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>9.789999999999999</v>
+        <v>20.31</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>5.43</v>
+        <v>12.79</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>2.37</v>
+        <v>3.44</v>
       </c>
       <c r="G120" s="6" t="n">
-        <v>1.99</v>
+        <v>4.07</v>
       </c>
       <c r="H120" s="6" t="n">
         <v>0</v>
@@ -6031,16 +6031,16 @@
         <v>0</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>5.43</v>
+        <v>12.79</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>2.37</v>
+        <v>3.44</v>
       </c>
       <c r="L120" s="6" t="n">
-        <v>9.789999999999999</v>
+        <v>20.31</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>14.21</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="121">
@@ -6060,16 +6060,16 @@
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>0</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>13.11</v>
@@ -6078,16 +6078,16 @@
         <v>0</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>13.11</v>
+        <v>18.73</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>13.11</v>
+        <v>23.07</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>10.89</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="122">
@@ -6145,47 +6145,94 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
           <t>72-1217</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>LCB</t>
         </is>
       </c>
-      <c r="D123" s="5" t="n">
+      <c r="D124" s="6" t="n">
         <v>3.77</v>
       </c>
-      <c r="E123" s="5" t="n">
+      <c r="E124" s="6" t="n">
         <v>1.38</v>
       </c>
-      <c r="F123" s="5" t="n">
+      <c r="F124" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="G123" s="5" t="n">
+      <c r="G124" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="H123" s="5" t="n">
+      <c r="H124" s="6" t="n">
         <v>5.35</v>
       </c>
-      <c r="I123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="5" t="n">
+      <c r="I124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="6" t="n">
         <v>6.72</v>
       </c>
-      <c r="K123" s="5" t="n">
+      <c r="K124" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="L123" s="5" t="n">
+      <c r="L124" s="6" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="M123" s="5" t="n">
+      <c r="M124" s="6" t="n">
         <v>14.88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M123"/>
+  <autoFilter ref="A4:M124"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:49</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>
@@ -3663,16 +3663,16 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>26.95</v>
+        <v>19.69</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>7.6</v>
+        <v>6.27</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>15.85</v>
+        <v>11.78</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>3.5</v>
+        <v>1.64</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
@@ -3681,16 +3681,16 @@
         <v>0</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>7.6</v>
+        <v>6.27</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>15.85</v>
+        <v>11.78</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>26.95</v>
+        <v>19.69</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>-2.95</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="71">

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Daily_Time_24h_Check" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M124"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>
@@ -5440,25 +5440,25 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>18.85</v>
+        <v>16.5</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>1.56</v>
+        <v>11.61</v>
       </c>
       <c r="G108" s="6" t="n">
-        <v>13.61</v>
+        <v>1.61</v>
       </c>
       <c r="H108" s="6" t="n">
         <v>0</v>
@@ -5467,45 +5467,45 @@
         <v>0</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>1.56</v>
+        <v>11.61</v>
       </c>
       <c r="L108" s="6" t="n">
-        <v>18.85</v>
+        <v>16.5</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>5.15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>16.5</v>
+        <v>18.35</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3.28</v>
+        <v>5.44</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>11.61</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.61</v>
+        <v>3.96</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>0</v>
@@ -5514,16 +5514,16 @@
         <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>3.28</v>
+        <v>5.44</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>11.61</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>16.5</v>
+        <v>18.35</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>7.5</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="110">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -5543,16 +5543,16 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>18.35</v>
+        <v>18.22</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>5.44</v>
+        <v>7.66</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>8.949999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="G110" s="6" t="n">
-        <v>3.96</v>
+        <v>3.44</v>
       </c>
       <c r="H110" s="6" t="n">
         <v>0</v>
@@ -5561,16 +5561,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>5.44</v>
+        <v>7.66</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>8.949999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="L110" s="6" t="n">
-        <v>18.35</v>
+        <v>18.22</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>5.65</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="111">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>18.22</v>
+        <v>21.08</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>7.66</v>
+        <v>8.5</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>7.12</v>
+        <v>8.01</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>3.44</v>
+        <v>4.57</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>0</v>
@@ -5608,16 +5608,16 @@
         <v>0</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>7.66</v>
+        <v>8.5</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>7.12</v>
+        <v>8.01</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>18.22</v>
+        <v>21.08</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>5.78</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="112">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -5637,16 +5637,16 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>21.08</v>
+        <v>19.32</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>8.5</v>
+        <v>12.75</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>8.01</v>
+        <v>2.68</v>
       </c>
       <c r="G112" s="6" t="n">
-        <v>4.57</v>
+        <v>3.9</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>0</v>
@@ -5655,16 +5655,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>8.5</v>
+        <v>12.75</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>8.01</v>
+        <v>2.68</v>
       </c>
       <c r="L112" s="6" t="n">
-        <v>21.08</v>
+        <v>19.32</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>2.92</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="113">
@@ -5675,25 +5675,25 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>19.32</v>
+        <v>17.35</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>12.75</v>
+        <v>7.33</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>2.68</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>3.9</v>
+        <v>1.63</v>
       </c>
       <c r="H113" s="5" t="n">
         <v>0</v>
@@ -5702,45 +5702,45 @@
         <v>0</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>12.75</v>
+        <v>7.33</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>2.68</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>19.32</v>
+        <v>17.35</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>4.68</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>17.35</v>
+        <v>11.92</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>7.33</v>
+        <v>3.66</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>8.380000000000001</v>
+        <v>6.14</v>
       </c>
       <c r="G114" s="6" t="n">
-        <v>1.63</v>
+        <v>2.13</v>
       </c>
       <c r="H114" s="6" t="n">
         <v>0</v>
@@ -5749,16 +5749,16 @@
         <v>0</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>7.33</v>
+        <v>3.66</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>8.380000000000001</v>
+        <v>6.14</v>
       </c>
       <c r="L114" s="6" t="n">
-        <v>17.35</v>
+        <v>11.92</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>6.65</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="115">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>11.92</v>
+        <v>23.52</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3.66</v>
+        <v>4.75</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>6.14</v>
+        <v>7.66</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2.13</v>
+        <v>11.11</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
@@ -5796,16 +5796,16 @@
         <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>3.66</v>
+        <v>4.75</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>6.14</v>
+        <v>7.66</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>11.92</v>
+        <v>23.52</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>12.08</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="116">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -5825,34 +5825,34 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>23.52</v>
+        <v>11.07</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>4.75</v>
+        <v>6.13</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>7.66</v>
+        <v>3.05</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>11.11</v>
+        <v>1.89</v>
       </c>
       <c r="H116" s="6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="I116" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>4.75</v>
+        <v>6.65</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>7.66</v>
+        <v>3.05</v>
       </c>
       <c r="L116" s="6" t="n">
-        <v>23.52</v>
+        <v>11.6</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>0.48</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="117">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -5872,34 +5872,34 @@
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>11.07</v>
+        <v>15.05</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>6.13</v>
+        <v>6.97</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>1.89</v>
+        <v>2.97</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="I117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>6.65</v>
+        <v>6.97</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>3.05</v>
+        <v>5.11</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>11.6</v>
+        <v>15.05</v>
       </c>
       <c r="M117" s="5" t="n">
-        <v>12.4</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -5910,25 +5910,25 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>15.05</v>
+        <v>32.17</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>6.97</v>
+        <v>9.98</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>5.11</v>
+        <v>18.74</v>
       </c>
       <c r="G118" s="6" t="n">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="H118" s="6" t="n">
         <v>0</v>
@@ -5937,63 +5937,63 @@
         <v>0</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>6.97</v>
+        <v>9.98</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>5.11</v>
+        <v>18.74</v>
       </c>
       <c r="L118" s="6" t="n">
-        <v>15.05</v>
+        <v>32.17</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>8.949999999999999</v>
+        <v>-8.17</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>32.17</v>
+        <v>20.31</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>9.98</v>
+        <v>12.79</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>18.74</v>
+        <v>3.44</v>
       </c>
       <c r="G119" s="5" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="K119" s="5" t="n">
         <v>3.44</v>
       </c>
-      <c r="H119" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="5" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="K119" s="5" t="n">
-        <v>18.74</v>
-      </c>
       <c r="L119" s="5" t="n">
-        <v>32.17</v>
+        <v>20.31</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>-8.17</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="120">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -6013,34 +6013,34 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>20.31</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>12.79</v>
+        <v>5.63</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="G120" s="6" t="n">
-        <v>4.07</v>
+        <v>1.55</v>
       </c>
       <c r="H120" s="6" t="n">
-        <v>0</v>
+        <v>13.11</v>
       </c>
       <c r="I120" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>12.79</v>
+        <v>18.73</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>3.44</v>
+        <v>2.79</v>
       </c>
       <c r="L120" s="6" t="n">
-        <v>20.31</v>
+        <v>23.07</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>3.69</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="121">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -6060,34 +6060,34 @@
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>13.11</v>
+        <v>0.61</v>
       </c>
       <c r="I121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>18.73</v>
+        <v>0.61</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>23.07</v>
+        <v>0.61</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>0.93</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="122">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -6107,34 +6107,34 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>0</v>
+        <v>15.44</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>0</v>
+        <v>12.56</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="G122" s="6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H122" s="6" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="I122" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>0.61</v>
+        <v>12.56</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="L122" s="6" t="n">
-        <v>0.61</v>
+        <v>15.44</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>23.39</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="123">
@@ -6145,94 +6145,47 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>15.44</v>
+        <v>3.77</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>12.56</v>
+        <v>1.38</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>12.56</v>
+        <v>6.72</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>1.08</v>
+        <v>0.6</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>15.44</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>8.56</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="E124" s="6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F124" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G124" s="6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H124" s="6" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="I124" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="6" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="K124" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L124" s="6" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="M124" s="6" t="n">
         <v>14.88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M124"/>
+  <autoFilter ref="A4:M123"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Daily_Time_24h_Check" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily_Time_24h_Check'!$A$4:$M$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 18:21</t>
+          <t>2026-08-04 14:01</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -608,16 +608,16 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>8.57</v>
+        <v>17.71</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5.4</v>
+        <v>8.73</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1.92</v>
+        <v>4.38</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
@@ -626,27 +626,27 @@
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>5.4</v>
+        <v>8.73</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>8.57</v>
+        <v>17.71</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>15.43</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -655,92 +655,92 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>18.68</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>3.5</v>
+        <v>7.76</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>9.539999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>13.04</v>
+        <v>18.68</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>10.96</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>23.21</v>
+        <v>22.68</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.61</v>
+        <v>3.37</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>19.9</v>
+        <v>17.64</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1.61</v>
+        <v>3.37</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>19.9</v>
+        <v>19.54</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>23.21</v>
+        <v>24.58</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.79</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>12.24</v>
+        <v>25.73</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7.63</v>
+        <v>15.64</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2.45</v>
+        <v>4.99</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0</v>
@@ -767,27 +767,27 @@
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>7.63</v>
+        <v>15.64</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>12.24</v>
+        <v>25.73</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>11.76</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8967</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -796,63 +796,63 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>26.68</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>12.58</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>12.24</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>17.93</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>12.24</v>
+        <v>0.04</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>32.03</v>
+        <v>0.04</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>-8.029999999999999</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>26.65</v>
+        <v>17.38</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>18.52</v>
+        <v>4.52</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>6.08</v>
+        <v>5.99</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>2.05</v>
+        <v>6.87</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0</v>
@@ -861,27 +861,27 @@
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>18.52</v>
+        <v>4.52</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>6.08</v>
+        <v>5.99</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>26.65</v>
+        <v>17.38</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>-2.65</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>7.85</v>
+        <v>20.4</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>5.22</v>
+        <v>9.4</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.82</v>
+        <v>1.86</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.81</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
@@ -908,139 +908,139 @@
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>5.22</v>
+        <v>9.4</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.82</v>
+        <v>1.86</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>7.85</v>
+        <v>20.4</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>16.15</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14.58</v>
+        <v>6.65</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>6.09</v>
+        <v>0.21</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>6.86</v>
+        <v>1.87</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1.63</v>
+        <v>4.56</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>7.64</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>6.09</v>
+        <v>7.86</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>6.86</v>
+        <v>1.87</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>14.58</v>
+        <v>14.29</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>9.42</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8004</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>37.14</v>
+        <v>19.27</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>34.14</v>
+        <v>12.58</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.74</v>
+        <v>4.02</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2.26</v>
+        <v>2.67</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>47.37</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>34.14</v>
+        <v>59.95</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.74</v>
+        <v>4.02</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>37.14</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>-13.14</v>
+        <v>-42.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>22.68</v>
+        <v>12.17</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>18.54</v>
+        <v>6.85</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3.21</v>
+        <v>2.19</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0</v>
@@ -1049,27 +1049,27 @@
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>18.54</v>
+        <v>6.85</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>22.68</v>
+        <v>12.17</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>1.32</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1219</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1078,63 +1078,63 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>22.03</v>
+        <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>11.51</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>11.51</v>
+        <v>0.08</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>22.03</v>
+        <v>0.08</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>1.97</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>35.65</v>
+        <v>15.81</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>22.42</v>
+        <v>4.3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>9.83</v>
+        <v>7.87</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0</v>
@@ -1143,45 +1143,45 @@
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>22.42</v>
+        <v>4.3</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>9.83</v>
+        <v>7.87</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>35.65</v>
+        <v>15.81</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-11.65</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>32.19</v>
+        <v>13.68</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>18.19</v>
+        <v>4.76</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>8.390000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>5.62</v>
+        <v>1.91</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
@@ -1190,45 +1190,45 @@
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>18.19</v>
+        <v>4.76</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>8.390000000000001</v>
+        <v>7.02</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>32.19</v>
+        <v>13.68</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>-8.19</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15.89</v>
+        <v>17.58</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>8.24</v>
+        <v>5.34</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>3.12</v>
+        <v>7.46</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4.53</v>
+        <v>4.79</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>0</v>
@@ -1237,45 +1237,45 @@
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>8.24</v>
+        <v>5.34</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>3.12</v>
+        <v>7.46</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>15.89</v>
+        <v>17.58</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>8.109999999999999</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>14.37</v>
+        <v>24.02</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>5.73</v>
+        <v>11.41</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>3.7</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>4.94</v>
+        <v>3.98</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
@@ -1284,27 +1284,27 @@
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>5.73</v>
+        <v>11.41</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>3.7</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>14.37</v>
+        <v>24.02</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>9.630000000000001</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>19.22</v>
+        <v>16.92</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7.04</v>
+        <v>9.49</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>10.08</v>
+        <v>3.58</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2.11</v>
+        <v>3.84</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
@@ -1331,92 +1331,92 @@
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>7.04</v>
+        <v>9.49</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>10.08</v>
+        <v>3.58</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>19.22</v>
+        <v>16.92</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>4.78</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>14.11</v>
+        <v>18.52</v>
       </c>
       <c r="E21" s="5" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="K21" s="5" t="n">
         <v>7.61</v>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>4.73</v>
-      </c>
       <c r="L21" s="5" t="n">
-        <v>14.11</v>
+        <v>19.38</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>9.890000000000001</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>18.8</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>7.61</v>
+        <v>5.41</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>8.57</v>
+        <v>1.46</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -1425,27 +1425,27 @@
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>7.61</v>
+        <v>5.41</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>8.57</v>
+        <v>1.46</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>18.8</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>5.2</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1454,45 +1454,45 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>30.03</v>
+        <v>9.51</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>8.9</v>
+        <v>6.74</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>18.47</v>
+        <v>1.17</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2.67</v>
+        <v>1.6</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0</v>
+        <v>8.68</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>8.9</v>
+        <v>15.42</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>18.47</v>
+        <v>1.17</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>30.03</v>
+        <v>18.19</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>-6.03</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>15</v>
+        <v>25.88</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5.78</v>
+        <v>14.12</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>6.55</v>
+        <v>4.41</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2.68</v>
+        <v>7.34</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>0</v>
@@ -1519,45 +1519,45 @@
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>5.78</v>
+        <v>14.12</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>6.55</v>
+        <v>4.41</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>15</v>
+        <v>25.88</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>9</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>22.04</v>
+        <v>25.1</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>11.33</v>
+        <v>11.64</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>6.72</v>
+        <v>5.94</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4</v>
+        <v>7.52</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0</v>
@@ -1566,45 +1566,45 @@
         <v>0</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>11.33</v>
+        <v>11.64</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>6.72</v>
+        <v>5.94</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>22.04</v>
+        <v>25.1</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>1.96</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>7.29</v>
+        <v>17.5</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>2.63</v>
+        <v>9.44</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>2.38</v>
+        <v>4.31</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
@@ -1613,27 +1613,27 @@
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>2.63</v>
+        <v>9.44</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>2.38</v>
+        <v>4.31</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>7.29</v>
+        <v>17.5</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>16.71</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>27.75</v>
+        <v>22.44</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>14.11</v>
+        <v>15.17</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>6.33</v>
+        <v>3.17</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>7.31</v>
+        <v>4.1</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
@@ -1660,27 +1660,27 @@
         <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>14.11</v>
+        <v>15.17</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>6.33</v>
+        <v>3.17</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>27.75</v>
+        <v>22.44</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>-3.75</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>19.15</v>
+        <v>9.19</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>14.59</v>
+        <v>3.97</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>2.46</v>
+        <v>3.51</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>2.09</v>
+        <v>1.71</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
@@ -1707,45 +1707,45 @@
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>14.59</v>
+        <v>3.97</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>2.46</v>
+        <v>3.51</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>19.15</v>
+        <v>9.19</v>
       </c>
       <c r="M28" s="6" t="n">
-        <v>4.85</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>24.51</v>
+        <v>14.11</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>7.61</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>12.94</v>
+        <v>2.86</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
@@ -1754,45 +1754,45 @@
         <v>0</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>7.61</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>12.94</v>
+        <v>2.86</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>24.51</v>
+        <v>14.11</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>-0.51</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>26.64</v>
+        <v>13.82</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>16.99</v>
+        <v>5.43</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>5.5</v>
+        <v>5.93</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4.16</v>
+        <v>2.46</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>0</v>
@@ -1801,27 +1801,27 @@
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>16.99</v>
+        <v>5.43</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>5.5</v>
+        <v>5.93</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>26.64</v>
+        <v>13.82</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-2.64</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>13.67</v>
+        <v>32.29</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>10.38</v>
+        <v>25.96</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.29</v>
+        <v>4.52</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
@@ -1848,27 +1848,27 @@
         <v>0</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>10.38</v>
+        <v>25.96</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>1.29</v>
+        <v>4.52</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>13.67</v>
+        <v>32.29</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>10.33</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1877,16 +1877,16 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>16.65</v>
+        <v>23.28</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>12.52</v>
+        <v>17.01</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>2.07</v>
+        <v>4.04</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>0</v>
@@ -1895,74 +1895,74 @@
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>12.52</v>
+        <v>17.01</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2.07</v>
+        <v>4.04</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>16.65</v>
+        <v>23.28</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>7.35</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>19.38</v>
+        <v>27.96</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>15.37</v>
+        <v>17.8</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.41</v>
+        <v>7.81</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>15.89</v>
+        <v>17.8</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>1.41</v>
+        <v>7.81</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>19.9</v>
+        <v>27.96</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>4.1</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>6.38</v>
+        <v>32.28</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>2.04</v>
+        <v>26.39</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>0</v>
@@ -1989,27 +1989,27 @@
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2.04</v>
+        <v>26.39</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>6.38</v>
+        <v>32.28</v>
       </c>
       <c r="M34" s="6" t="n">
-        <v>17.62</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2018,16 +2018,16 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>17.85</v>
+        <v>17.49</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>8.26</v>
+        <v>10.71</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>5.43</v>
+        <v>3.65</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>4.17</v>
+        <v>3.12</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>0</v>
@@ -2036,92 +2036,92 @@
         <v>0</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>8.26</v>
+        <v>10.71</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>5.43</v>
+        <v>3.65</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>17.85</v>
+        <v>17.49</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>6.15</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>71-8683</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1.49</v>
+        <v>3.32</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>1.49</v>
+        <v>14.25</v>
       </c>
       <c r="M36" s="6" t="n">
-        <v>22.51</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>16.45</v>
+        <v>17.39</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>4.25</v>
+        <v>9.94</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>10.67</v>
+        <v>3.73</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.53</v>
+        <v>3.71</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>0</v>
@@ -2130,27 +2130,27 @@
         <v>0</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>4.25</v>
+        <v>9.94</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>10.67</v>
+        <v>3.73</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>16.45</v>
+        <v>17.39</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>7.55</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2159,16 +2159,16 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>23.9</v>
+        <v>16.18</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>13.83</v>
+        <v>10.28</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>4.16</v>
+        <v>2.37</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>5.92</v>
+        <v>3.54</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0</v>
@@ -2177,92 +2177,92 @@
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>13.83</v>
+        <v>10.28</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>4.16</v>
+        <v>2.37</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>23.9</v>
+        <v>16.18</v>
       </c>
       <c r="M38" s="6" t="n">
-        <v>0.1</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-0419</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>29.74</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>21.91</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>21.91</v>
+        <v>0</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>4.07</v>
+        <v>0.04</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>29.74</v>
+        <v>0.04</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>-5.74</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>22.21</v>
+        <v>40.14</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>14.16</v>
+        <v>16.42</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>4.87</v>
+        <v>20.07</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0</v>
@@ -2271,27 +2271,27 @@
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>14.16</v>
+        <v>16.42</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>4.87</v>
+        <v>20.07</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>22.21</v>
+        <v>40.14</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>1.79</v>
+        <v>-16.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2300,16 +2300,16 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>27.43</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>4.26</v>
+        <v>22.18</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>2.45</v>
+        <v>3.21</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>0</v>
@@ -2318,22 +2318,22 @@
         <v>0</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>4.26</v>
+        <v>22.18</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>2.45</v>
+        <v>3.21</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>8.960000000000001</v>
+        <v>27.43</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>15.04</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2347,45 +2347,45 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>23.94</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>23.94</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.37</v>
+        <v>9.85</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.37</v>
+        <v>39.1</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>23.63</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2394,16 +2394,16 @@
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>9.66</v>
+        <v>19.74</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>6.21</v>
+        <v>14.64</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>1.6</v>
+        <v>2.93</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>0</v>
@@ -2412,45 +2412,45 @@
         <v>0</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>6.21</v>
+        <v>14.64</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>1.6</v>
+        <v>2.93</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>9.66</v>
+        <v>19.74</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>14.34</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>19.71</v>
+        <v>37.47</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>12.69</v>
+        <v>24.4</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>3.78</v>
+        <v>8.6</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>3.23</v>
+        <v>4.47</v>
       </c>
       <c r="H44" s="6" t="n">
         <v>0</v>
@@ -2459,22 +2459,22 @@
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>12.69</v>
+        <v>24.4</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>3.78</v>
+        <v>8.6</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>19.71</v>
+        <v>37.47</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>4.29</v>
+        <v>-13.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2488,45 +2488,45 @@
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>20.16</v>
+        <v>11.34</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5.72</v>
+        <v>4.73</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>10</v>
+        <v>3.05</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>5.72</v>
+        <v>10.84</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>20.16</v>
+        <v>17.44</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>3.84</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>26.48</v>
+        <v>14.59</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>3.64</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>13.45</v>
+        <v>4.25</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>3.84</v>
+        <v>6.69</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>0</v>
@@ -2553,27 +2553,27 @@
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>3.64</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>13.45</v>
+        <v>4.25</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>26.48</v>
+        <v>14.59</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>-2.48</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>12.93</v>
+        <v>6.08</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>6.21</v>
+        <v>1.24</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>4.8</v>
+        <v>3.07</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>0</v>
@@ -2600,45 +2600,45 @@
         <v>0</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>6.21</v>
+        <v>1.24</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>4.8</v>
+        <v>3.07</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>12.93</v>
+        <v>6.08</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>11.07</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>22.85</v>
+        <v>20.82</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>13.39</v>
+        <v>9.33</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>5.66</v>
+        <v>7.05</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>3.8</v>
+        <v>4.44</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>0</v>
@@ -2647,27 +2647,27 @@
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>13.39</v>
+        <v>9.33</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>5.66</v>
+        <v>7.05</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>22.85</v>
+        <v>20.82</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>1.15</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -2676,16 +2676,16 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>21.67</v>
+        <v>13.97</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>6.68</v>
+        <v>4.59</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>13.43</v>
+        <v>5.22</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1.57</v>
+        <v>4.15</v>
       </c>
       <c r="H49" s="5" t="n">
         <v>0</v>
@@ -2694,27 +2694,27 @@
         <v>0</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>6.68</v>
+        <v>4.59</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>13.43</v>
+        <v>5.22</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>21.67</v>
+        <v>13.97</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>2.33</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2723,16 +2723,16 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>4.35</v>
+        <v>10.21</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>6.98</v>
+        <v>3.56</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>3.77</v>
+        <v>3.53</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
@@ -2741,27 +2741,27 @@
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>4.35</v>
+        <v>10.21</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>6.98</v>
+        <v>3.56</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -2770,16 +2770,16 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>24.81</v>
+        <v>29.46</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2.76</v>
+        <v>15.77</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>19.43</v>
+        <v>4.18</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>2.62</v>
+        <v>9.51</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>0</v>
@@ -2788,45 +2788,45 @@
         <v>0</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>2.76</v>
+        <v>15.77</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>19.43</v>
+        <v>4.18</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>24.81</v>
+        <v>29.46</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>13.83</v>
+        <v>34.29</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>10.75</v>
+        <v>21.43</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1.23</v>
+        <v>6.7</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>1.86</v>
+        <v>6.15</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
@@ -2835,27 +2835,27 @@
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>10.75</v>
+        <v>21.43</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>1.23</v>
+        <v>6.7</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>13.83</v>
+        <v>34.29</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>10.17</v>
+        <v>-10.29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -2864,16 +2864,16 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>25.37</v>
+        <v>34.51</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>13.71</v>
+        <v>20.54</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>8.08</v>
+        <v>5.29</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>3.58</v>
+        <v>8.69</v>
       </c>
       <c r="H53" s="5" t="n">
         <v>0</v>
@@ -2882,45 +2882,45 @@
         <v>0</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>13.71</v>
+        <v>20.54</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>8.08</v>
+        <v>5.29</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>25.37</v>
+        <v>34.51</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>-1.37</v>
+        <v>-10.51</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>28.07</v>
+        <v>29.43</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>19.07</v>
+        <v>16.57</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>4.98</v>
+        <v>7.13</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>4.01</v>
+        <v>5.72</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
@@ -2929,27 +2929,27 @@
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>19.07</v>
+        <v>16.57</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>4.98</v>
+        <v>7.13</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>28.07</v>
+        <v>29.43</v>
       </c>
       <c r="M54" s="6" t="n">
-        <v>-4.07</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2958,16 +2958,16 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>11.28</v>
+        <v>11.97</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>5.02</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>4.69</v>
+        <v>1.63</v>
       </c>
       <c r="H55" s="5" t="n">
         <v>0</v>
@@ -2976,27 +2976,27 @@
         <v>0</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>5.02</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>11.28</v>
+        <v>11.97</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>12.72</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -3005,63 +3005,63 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>6.74</v>
+        <v>14.48</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>4.28</v>
+        <v>12.17</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="H56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>4.28</v>
+        <v>12.17</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>1.36</v>
+        <v>0.7</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>7.46</v>
+        <v>14.48</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>16.54</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>8.98</v>
+        <v>31.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>6.37</v>
+        <v>25.05</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>1.05</v>
+        <v>4.84</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>0</v>
@@ -3070,27 +3070,27 @@
         <v>0</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>6.37</v>
+        <v>25.05</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>1.05</v>
+        <v>4.84</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>8.98</v>
+        <v>31.43</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>15.02</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -3099,16 +3099,16 @@
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>11.17</v>
+        <v>31.52</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>3.44</v>
+        <v>24.38</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0</v>
@@ -3117,27 +3117,27 @@
         <v>0</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>3.44</v>
+        <v>24.38</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>11.17</v>
+        <v>31.52</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>12.83</v>
+        <v>-7.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3146,16 +3146,16 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>31.78</v>
+        <v>25.95</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>23.53</v>
+        <v>21.98</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>4.82</v>
+        <v>2.25</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>3.43</v>
+        <v>1.72</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>0</v>
@@ -3164,27 +3164,27 @@
         <v>0</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>23.53</v>
+        <v>21.98</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>4.82</v>
+        <v>2.25</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>31.78</v>
+        <v>25.95</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>-7.78</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -3193,16 +3193,16 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>13.24</v>
+        <v>31.5</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>8.58</v>
+        <v>28.4</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>2.57</v>
+        <v>0.96</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>0</v>
@@ -3211,45 +3211,45 @@
         <v>0</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>8.58</v>
+        <v>28.4</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>2.57</v>
+        <v>0.96</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>13.24</v>
+        <v>31.5</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>10.76</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>18.4</v>
+        <v>41.61</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>7.6</v>
+        <v>35.5</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>6.93</v>
+        <v>2.03</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>3.87</v>
+        <v>4.08</v>
       </c>
       <c r="H61" s="5" t="n">
         <v>0</v>
@@ -3258,22 +3258,22 @@
         <v>0</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>7.6</v>
+        <v>35.5</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>6.93</v>
+        <v>2.03</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>18.4</v>
+        <v>41.61</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>5.6</v>
+        <v>-17.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3287,40 +3287,40 @@
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0</v>
+        <v>15.62</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0</v>
+        <v>12.65</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>1.6</v>
+        <v>12.65</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>1.6</v>
+        <v>15.62</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>22.4</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -3334,40 +3334,40 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>6.93</v>
+        <v>31.62</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.27</v>
+        <v>13.34</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.05</v>
+        <v>14.81</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>6.61</v>
+        <v>3.47</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>19.47</v>
+        <v>0</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>3.14</v>
+        <v>13.34</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>19.52</v>
+        <v>14.81</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>29.27</v>
+        <v>31.62</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>-5.27</v>
+        <v>-7.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>27.41</v>
+        <v>10.84</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>11.36</v>
+        <v>6.65</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>11.35</v>
+        <v>2.61</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>4.7</v>
+        <v>1.58</v>
       </c>
       <c r="H64" s="6" t="n">
         <v>0</v>
@@ -3399,27 +3399,27 @@
         <v>0</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>11.36</v>
+        <v>6.65</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>11.35</v>
+        <v>2.61</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>27.41</v>
+        <v>10.84</v>
       </c>
       <c r="M64" s="6" t="n">
-        <v>-3.41</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>13.31</v>
+        <v>17.24</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>7.37</v>
+        <v>4.94</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>4.29</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>0</v>
@@ -3446,22 +3446,22 @@
         <v>0</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>7.37</v>
+        <v>4.94</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>4.29</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>13.31</v>
+        <v>17.24</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>10.69</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -3475,16 +3475,16 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>19.97</v>
+        <v>15.61</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>11.82</v>
+        <v>4.05</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>6.15</v>
+        <v>10.09</v>
       </c>
       <c r="G66" s="6" t="n">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="H66" s="6" t="n">
         <v>0</v>
@@ -3493,27 +3493,27 @@
         <v>0</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>11.82</v>
+        <v>4.05</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>6.15</v>
+        <v>10.09</v>
       </c>
       <c r="L66" s="6" t="n">
-        <v>19.97</v>
+        <v>15.61</v>
       </c>
       <c r="M66" s="6" t="n">
-        <v>4.03</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1219</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3522,45 +3522,45 @@
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>26.52</v>
+        <v>0</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>13.27</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>13.27</v>
+        <v>0</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>8.779999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>26.52</v>
+        <v>0.03</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-2.52</v>
+        <v>23.97</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -3569,45 +3569,45 @@
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>8.92</v>
+        <v>27.04</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>3.05</v>
+        <v>5.96</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>3.87</v>
+        <v>18</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>2</v>
+        <v>3.08</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3.05</v>
+        <v>5.96</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>3.89</v>
+        <v>18</v>
       </c>
       <c r="L68" s="6" t="n">
-        <v>8.94</v>
+        <v>27.04</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>15.06</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -3616,16 +3616,16 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>16.04</v>
+        <v>11.16</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>6.71</v>
+        <v>1.64</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>4.76</v>
+        <v>7.39</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>4.57</v>
+        <v>2.13</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>0</v>
@@ -3634,27 +3634,27 @@
         <v>0</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>6.71</v>
+        <v>1.64</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>4.76</v>
+        <v>7.39</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>16.04</v>
+        <v>11.16</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>7.96</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -3663,16 +3663,16 @@
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>19.69</v>
+        <v>34.34</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>6.27</v>
+        <v>5.96</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>11.78</v>
+        <v>20.12</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>1.64</v>
+        <v>8.25</v>
       </c>
       <c r="H70" s="6" t="n">
         <v>0</v>
@@ -3681,27 +3681,27 @@
         <v>0</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>6.27</v>
+        <v>5.96</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>11.78</v>
+        <v>20.12</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>19.69</v>
+        <v>34.34</v>
       </c>
       <c r="M70" s="6" t="n">
-        <v>4.31</v>
+        <v>-10.34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>23.92</v>
+        <v>26.47</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5.86</v>
+        <v>2.31</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>15.77</v>
+        <v>15.3</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>2.29</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>0</v>
@@ -3728,45 +3728,45 @@
         <v>0</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>5.86</v>
+        <v>2.31</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>15.77</v>
+        <v>15.3</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>23.92</v>
+        <v>26.47</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.08</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>22.61</v>
+        <v>21.51</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>5.66</v>
+        <v>4.41</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>15.29</v>
+        <v>11.11</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>1.66</v>
+        <v>6</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>0</v>
@@ -3775,27 +3775,27 @@
         <v>0</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>5.66</v>
+        <v>4.41</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>15.29</v>
+        <v>11.11</v>
       </c>
       <c r="L72" s="6" t="n">
-        <v>22.61</v>
+        <v>21.51</v>
       </c>
       <c r="M72" s="6" t="n">
-        <v>1.39</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>15.12</v>
+        <v>22.42</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>5.1</v>
+        <v>3.36</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>5.37</v>
+        <v>17.53</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>4.65</v>
+        <v>1.53</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>0</v>
@@ -3822,27 +3822,27 @@
         <v>0</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>5.1</v>
+        <v>3.36</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>5.37</v>
+        <v>17.53</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>15.12</v>
+        <v>22.42</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>8.880000000000001</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -3851,16 +3851,16 @@
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>12.64</v>
+        <v>23.94</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>7.8</v>
+        <v>10.55</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.6</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>3.24</v>
+        <v>5.24</v>
       </c>
       <c r="H74" s="6" t="n">
         <v>0</v>
@@ -3869,27 +3869,27 @@
         <v>0</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>7.8</v>
+        <v>10.55</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1.6</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L74" s="6" t="n">
-        <v>12.64</v>
+        <v>23.94</v>
       </c>
       <c r="M74" s="6" t="n">
-        <v>11.36</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3898,16 +3898,16 @@
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>14.6</v>
+        <v>23.35</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>5.66</v>
+        <v>17.67</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="H75" s="5" t="n">
         <v>0</v>
@@ -3916,22 +3916,22 @@
         <v>0</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>5.66</v>
+        <v>17.67</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>14.6</v>
+        <v>23.35</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>9.4</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -3945,16 +3945,16 @@
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>18.89</v>
+        <v>23.64</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>3.62</v>
+        <v>5.47</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>13.17</v>
+        <v>11.83</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>2.1</v>
+        <v>6.34</v>
       </c>
       <c r="H76" s="6" t="n">
         <v>0</v>
@@ -3963,27 +3963,27 @@
         <v>0</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>3.62</v>
+        <v>5.47</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>13.17</v>
+        <v>11.83</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>18.89</v>
+        <v>23.64</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>5.11</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8682</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -3992,45 +3992,45 @@
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>27.06</v>
+        <v>0</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>19.86</v>
+        <v>0</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="H77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>19.86</v>
+        <v>0</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>4.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>27.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-3.06</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -4039,16 +4039,16 @@
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>9.390000000000001</v>
+        <v>18.15</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1.89</v>
+        <v>2.93</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>2.48</v>
+        <v>10.13</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>5.01</v>
+        <v>5.09</v>
       </c>
       <c r="H78" s="6" t="n">
         <v>0</v>
@@ -4057,27 +4057,27 @@
         <v>0</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>1.89</v>
+        <v>2.93</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>2.48</v>
+        <v>10.13</v>
       </c>
       <c r="L78" s="6" t="n">
-        <v>9.390000000000001</v>
+        <v>18.15</v>
       </c>
       <c r="M78" s="6" t="n">
-        <v>14.61</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4086,45 +4086,45 @@
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>9.800000000000001</v>
+        <v>19.62</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>4.13</v>
+        <v>3.63</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>3.19</v>
+        <v>13.74</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="H79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>4.13</v>
+        <v>3.63</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>3.69</v>
+        <v>13.74</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>10.31</v>
+        <v>19.62</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>13.69</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -4133,40 +4133,40 @@
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>12.64</v>
+        <v>32.66</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>3.69</v>
+        <v>4.75</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>6.64</v>
+        <v>26.25</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="I80" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>12.85</v>
+        <v>4.75</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>6.64</v>
+        <v>26.25</v>
       </c>
       <c r="L80" s="6" t="n">
-        <v>21.8</v>
+        <v>32.66</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>2.2</v>
+        <v>-8.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -4180,16 +4180,16 @@
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>26.63</v>
+        <v>19.83</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>8.470000000000001</v>
+        <v>13.65</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>13.89</v>
+        <v>2.13</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="H81" s="5" t="n">
         <v>0</v>
@@ -4198,45 +4198,45 @@
         <v>0</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>8.470000000000001</v>
+        <v>13.65</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>13.89</v>
+        <v>2.13</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>26.63</v>
+        <v>19.83</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-2.63</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>12.77</v>
+        <v>21.18</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>1.8</v>
+        <v>7.52</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>9.25</v>
+        <v>12.12</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="H82" s="6" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
         <v>0</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>1.8</v>
+        <v>7.52</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>9.25</v>
+        <v>12.12</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>12.77</v>
+        <v>21.18</v>
       </c>
       <c r="M82" s="6" t="n">
-        <v>11.23</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
@@ -4274,16 +4274,16 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>26.03</v>
+        <v>14.87</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>8.710000000000001</v>
+        <v>2.77</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>13.29</v>
+        <v>8.9</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>4.03</v>
+        <v>3.21</v>
       </c>
       <c r="H83" s="5" t="n">
         <v>0</v>
@@ -4292,22 +4292,22 @@
         <v>0</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>8.710000000000001</v>
+        <v>2.77</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>13.29</v>
+        <v>8.9</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>26.03</v>
+        <v>14.87</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>-2.03</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>15.77</v>
+        <v>32.58</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>3.53</v>
+        <v>11.91</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>10.61</v>
+        <v>16.07</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>1.64</v>
+        <v>4.6</v>
       </c>
       <c r="H84" s="6" t="n">
         <v>0</v>
@@ -4339,27 +4339,27 @@
         <v>0</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>3.53</v>
+        <v>11.91</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>10.61</v>
+        <v>16.07</v>
       </c>
       <c r="L84" s="6" t="n">
-        <v>15.77</v>
+        <v>32.58</v>
       </c>
       <c r="M84" s="6" t="n">
-        <v>8.23</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -4368,40 +4368,40 @@
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>4.69</v>
+        <v>40.27</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0.13</v>
+        <v>6.89</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>2.81</v>
+        <v>23.69</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1.75</v>
+        <v>9.69</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>7.13</v>
+        <v>6.89</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>2.81</v>
+        <v>23.69</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>11.7</v>
+        <v>40.27</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>12.3</v>
+        <v>-16.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
@@ -4415,16 +4415,16 @@
         </is>
       </c>
       <c r="D86" s="6" t="n">
-        <v>14.2</v>
+        <v>29.2</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>5.16</v>
+        <v>10.17</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>7.37</v>
+        <v>13.66</v>
       </c>
       <c r="G86" s="6" t="n">
-        <v>1.67</v>
+        <v>5.37</v>
       </c>
       <c r="H86" s="6" t="n">
         <v>0</v>
@@ -4433,27 +4433,27 @@
         <v>0</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>5.16</v>
+        <v>10.17</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>7.37</v>
+        <v>13.66</v>
       </c>
       <c r="L86" s="6" t="n">
-        <v>14.2</v>
+        <v>29.2</v>
       </c>
       <c r="M86" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1219</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -4462,45 +4462,45 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>21.53</v>
+        <v>0</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I87" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>10.4</v>
+        <v>0.04</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>21.53</v>
+        <v>0.04</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>2.47</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -4509,16 +4509,16 @@
         </is>
       </c>
       <c r="D88" s="6" t="n">
-        <v>10.65</v>
+        <v>19.59</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>5.46</v>
+        <v>9.34</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>3.53</v>
+        <v>6.81</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>1.66</v>
+        <v>3.44</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>0</v>
@@ -4527,27 +4527,27 @@
         <v>0</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>5.46</v>
+        <v>9.34</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>3.53</v>
+        <v>6.81</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>10.65</v>
+        <v>19.59</v>
       </c>
       <c r="M88" s="6" t="n">
-        <v>13.35</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -4556,45 +4556,45 @@
         </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>19.98</v>
+        <v>20.36</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>11.59</v>
+        <v>8.52</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>4.56</v>
+        <v>6.79</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>3.84</v>
+        <v>5.05</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>11.59</v>
+        <v>8.52</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>5.68</v>
+        <v>6.79</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>21.1</v>
+        <v>20.36</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>2.9</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -4603,16 +4603,16 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>7.56</v>
+        <v>19.97</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>3.95</v>
+        <v>10.89</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>2.73</v>
+        <v>7.99</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0</v>
@@ -4621,27 +4621,27 @@
         <v>0</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>3.95</v>
+        <v>10.89</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>0.89</v>
+        <v>1.09</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>7.56</v>
+        <v>19.97</v>
       </c>
       <c r="M90" s="6" t="n">
-        <v>16.44</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -4650,16 +4650,16 @@
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>22.16</v>
+        <v>17.96</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>13.02</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>3.74</v>
+        <v>4.28</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>0</v>
@@ -4668,45 +4668,45 @@
         <v>0</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>13.02</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>22.16</v>
+        <v>17.96</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>1.84</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D92" s="6" t="n">
-        <v>25.17</v>
+        <v>13.15</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>11.43</v>
+        <v>6.45</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>10.48</v>
+        <v>4.21</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>3.26</v>
+        <v>2.49</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>0</v>
@@ -4715,27 +4715,27 @@
         <v>0</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>11.43</v>
+        <v>6.45</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>10.48</v>
+        <v>4.21</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>25.17</v>
+        <v>13.15</v>
       </c>
       <c r="M92" s="6" t="n">
-        <v>-1.17</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -4744,16 +4744,16 @@
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>13.45</v>
+        <v>22.49</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>3.04</v>
+        <v>11.93</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7.73</v>
+        <v>7.49</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>2.68</v>
+        <v>3.07</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>0</v>
@@ -4762,27 +4762,27 @@
         <v>0</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>3.04</v>
+        <v>11.93</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>7.73</v>
+        <v>7.49</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>13.45</v>
+        <v>22.49</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>10.55</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -4791,16 +4791,16 @@
         </is>
       </c>
       <c r="D94" s="6" t="n">
-        <v>13.4</v>
+        <v>15.34</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1.31</v>
+        <v>12.57</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>8.49</v>
+        <v>0.71</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="H94" s="6" t="n">
         <v>0</v>
@@ -4809,27 +4809,27 @@
         <v>0</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>1.31</v>
+        <v>12.57</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>8.49</v>
+        <v>0.71</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>13.4</v>
+        <v>15.34</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>10.6</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -4838,16 +4838,16 @@
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>21.35</v>
+        <v>10.94</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>5.45</v>
+        <v>4.33</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>8.720000000000001</v>
+        <v>4.17</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>7.18</v>
+        <v>2.44</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>0</v>
@@ -4856,45 +4856,45 @@
         <v>0</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>5.45</v>
+        <v>4.33</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>8.720000000000001</v>
+        <v>4.17</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>21.35</v>
+        <v>10.94</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>2.65</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>31.63</v>
+        <v>16.73</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>5.08</v>
+        <v>13.54</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>13.47</v>
+        <v>0.91</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>13.07</v>
+        <v>2.28</v>
       </c>
       <c r="H96" s="6" t="n">
         <v>0</v>
@@ -4903,27 +4903,27 @@
         <v>0</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>5.08</v>
+        <v>13.54</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>13.47</v>
+        <v>0.91</v>
       </c>
       <c r="L96" s="6" t="n">
-        <v>31.63</v>
+        <v>16.73</v>
       </c>
       <c r="M96" s="6" t="n">
-        <v>-7.63</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -4932,16 +4932,16 @@
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>23.21</v>
+        <v>12.03</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>11.32</v>
+        <v>9.74</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>10.1</v>
+        <v>0.82</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>0</v>
@@ -4950,27 +4950,27 @@
         <v>0</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>11.32</v>
+        <v>9.74</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>10.1</v>
+        <v>0.82</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>23.21</v>
+        <v>12.03</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>0.79</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -4979,16 +4979,16 @@
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>13.43</v>
+        <v>27.18</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>2.56</v>
+        <v>4.67</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>9</v>
+        <v>20.25</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="H98" s="6" t="n">
         <v>0</v>
@@ -4997,27 +4997,27 @@
         <v>0</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>2.56</v>
+        <v>4.67</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>9</v>
+        <v>20.25</v>
       </c>
       <c r="L98" s="6" t="n">
-        <v>13.43</v>
+        <v>27.18</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>10.57</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -5026,16 +5026,16 @@
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>10.37</v>
+        <v>26.24</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1.89</v>
+        <v>4.18</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>6.57</v>
+        <v>19.08</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1.91</v>
+        <v>2.99</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0</v>
@@ -5044,22 +5044,22 @@
         <v>0</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>1.89</v>
+        <v>4.18</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>6.57</v>
+        <v>19.08</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>10.37</v>
+        <v>26.24</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>13.63</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -5073,16 +5073,16 @@
         </is>
       </c>
       <c r="D100" s="6" t="n">
-        <v>21.15</v>
+        <v>25.29</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>14.34</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>11.19</v>
+        <v>5.88</v>
       </c>
       <c r="G100" s="6" t="n">
-        <v>1.66</v>
+        <v>5.07</v>
       </c>
       <c r="H100" s="6" t="n">
         <v>0</v>
@@ -5091,22 +5091,22 @@
         <v>0</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>8.300000000000001</v>
+        <v>14.34</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>11.19</v>
+        <v>5.88</v>
       </c>
       <c r="L100" s="6" t="n">
-        <v>21.15</v>
+        <v>25.29</v>
       </c>
       <c r="M100" s="6" t="n">
-        <v>2.85</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>17.76</v>
+        <v>25.4</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>10.02</v>
+        <v>4.44</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>5.61</v>
+        <v>18.91</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="H101" s="5" t="n">
         <v>0</v>
@@ -5138,27 +5138,27 @@
         <v>0</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>10.02</v>
+        <v>4.44</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>5.61</v>
+        <v>18.91</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>17.76</v>
+        <v>25.4</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>6.24</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -5167,16 +5167,16 @@
         </is>
       </c>
       <c r="D102" s="6" t="n">
-        <v>38.11</v>
+        <v>12.56</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>4.4</v>
+        <v>5.76</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>32.02</v>
+        <v>5.03</v>
       </c>
       <c r="G102" s="6" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>0</v>
@@ -5185,45 +5185,45 @@
         <v>0</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>4.4</v>
+        <v>5.76</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>32.02</v>
+        <v>5.03</v>
       </c>
       <c r="L102" s="6" t="n">
-        <v>38.11</v>
+        <v>12.56</v>
       </c>
       <c r="M102" s="6" t="n">
-        <v>-14.11</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>32.1</v>
+        <v>20.75</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2.97</v>
+        <v>6.71</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>27.39</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.74</v>
+        <v>4.15</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>0</v>
@@ -5232,27 +5232,27 @@
         <v>0</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>2.97</v>
+        <v>6.71</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>27.39</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>32.1</v>
+        <v>20.75</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>-8.1</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -5261,45 +5261,45 @@
         </is>
       </c>
       <c r="D104" s="6" t="n">
-        <v>0</v>
+        <v>26.14</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0</v>
+        <v>14.49</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>3.15</v>
+        <v>14.49</v>
       </c>
       <c r="L104" s="6" t="n">
-        <v>3.15</v>
+        <v>26.14</v>
       </c>
       <c r="M104" s="6" t="n">
-        <v>20.85</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -5308,16 +5308,16 @@
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>31.74</v>
+        <v>15.25</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>19.06</v>
+        <v>11.1</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>10.8</v>
+        <v>1.01</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1.89</v>
+        <v>3.14</v>
       </c>
       <c r="H105" s="5" t="n">
         <v>0</v>
@@ -5326,27 +5326,27 @@
         <v>0</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>19.06</v>
+        <v>11.1</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>10.8</v>
+        <v>1.01</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>31.74</v>
+        <v>15.25</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>-7.74</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -5355,16 +5355,16 @@
         </is>
       </c>
       <c r="D106" s="6" t="n">
-        <v>19.5</v>
+        <v>40.14</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>5.69</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>10.31</v>
+        <v>26.67</v>
       </c>
       <c r="G106" s="6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H106" s="6" t="n">
         <v>0</v>
@@ -5373,92 +5373,92 @@
         <v>0</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>5.69</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>10.31</v>
+        <v>26.67</v>
       </c>
       <c r="L106" s="6" t="n">
-        <v>19.5</v>
+        <v>40.14</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>4.5</v>
+        <v>-16.14</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8681</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>21.49</v>
+        <v>0</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>7.63</v>
+        <v>0</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>9.289999999999999</v>
+        <v>0</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>7.63</v>
+        <v>0</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>9.289999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>21.49</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>2.51</v>
+        <v>23.93</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D108" s="6" t="n">
-        <v>16.5</v>
+        <v>16.98</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>3.28</v>
+        <v>7.09</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>11.61</v>
+        <v>8.32</v>
       </c>
       <c r="G108" s="6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H108" s="6" t="n">
         <v>0</v>
@@ -5467,27 +5467,27 @@
         <v>0</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>3.28</v>
+        <v>7.09</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>11.61</v>
+        <v>8.32</v>
       </c>
       <c r="L108" s="6" t="n">
-        <v>16.5</v>
+        <v>16.98</v>
       </c>
       <c r="M108" s="6" t="n">
-        <v>7.5</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -5496,16 +5496,16 @@
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>18.35</v>
+        <v>25.41</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>5.44</v>
+        <v>12.46</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>8.949999999999999</v>
+        <v>11.48</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>3.96</v>
+        <v>1.48</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>0</v>
@@ -5514,27 +5514,27 @@
         <v>0</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>5.44</v>
+        <v>12.46</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>8.949999999999999</v>
+        <v>11.48</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>18.35</v>
+        <v>25.41</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>5.65</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -5543,16 +5543,16 @@
         </is>
       </c>
       <c r="D110" s="6" t="n">
-        <v>18.22</v>
+        <v>36.86</v>
       </c>
       <c r="E110" s="6" t="n">
-        <v>7.66</v>
+        <v>6.89</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>7.12</v>
+        <v>27.15</v>
       </c>
       <c r="G110" s="6" t="n">
-        <v>3.44</v>
+        <v>2.82</v>
       </c>
       <c r="H110" s="6" t="n">
         <v>0</v>
@@ -5561,27 +5561,27 @@
         <v>0</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>7.66</v>
+        <v>6.89</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>7.12</v>
+        <v>27.15</v>
       </c>
       <c r="L110" s="6" t="n">
-        <v>18.22</v>
+        <v>36.86</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>5.78</v>
+        <v>-12.86</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>21.08</v>
+        <v>37.9</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>8.5</v>
+        <v>8.93</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>8.01</v>
+        <v>27.2</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>4.57</v>
+        <v>1.77</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>0</v>
@@ -5608,22 +5608,22 @@
         <v>0</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>8.5</v>
+        <v>8.93</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>8.01</v>
+        <v>27.2</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>21.08</v>
+        <v>37.9</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>2.92</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
@@ -5637,16 +5637,16 @@
         </is>
       </c>
       <c r="D112" s="6" t="n">
-        <v>19.32</v>
+        <v>36.28</v>
       </c>
       <c r="E112" s="6" t="n">
-        <v>12.75</v>
+        <v>9.76</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>2.68</v>
+        <v>24.2</v>
       </c>
       <c r="G112" s="6" t="n">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>0</v>
@@ -5655,45 +5655,45 @@
         <v>0</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>12.75</v>
+        <v>9.76</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>2.68</v>
+        <v>24.2</v>
       </c>
       <c r="L112" s="6" t="n">
-        <v>19.32</v>
+        <v>36.28</v>
       </c>
       <c r="M112" s="6" t="n">
-        <v>4.68</v>
+        <v>-12.28</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>17.35</v>
+        <v>14.56</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>7.33</v>
+        <v>4.32</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="H113" s="5" t="n">
         <v>0</v>
@@ -5702,27 +5702,27 @@
         <v>0</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>7.33</v>
+        <v>4.32</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>17.35</v>
+        <v>14.56</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>6.65</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -5731,40 +5731,40 @@
         </is>
       </c>
       <c r="D114" s="6" t="n">
-        <v>11.92</v>
+        <v>54.1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>3.66</v>
+        <v>15.59</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>6.14</v>
+        <v>36.57</v>
       </c>
       <c r="G114" s="6" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="I114" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>3.66</v>
+        <v>19.31</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>6.14</v>
+        <v>36.57</v>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11.92</v>
+        <v>57.82</v>
       </c>
       <c r="M114" s="6" t="n">
-        <v>12.08</v>
+        <v>-33.82</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -5778,16 +5778,16 @@
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>23.52</v>
+        <v>23.36</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4.75</v>
+        <v>1.29</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>7.66</v>
+        <v>14.81</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>11.11</v>
+        <v>7.26</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>0</v>
@@ -5796,22 +5796,22 @@
         <v>0</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>4.75</v>
+        <v>1.29</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>7.66</v>
+        <v>14.81</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>23.52</v>
+        <v>23.36</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
@@ -5825,40 +5825,40 @@
         </is>
       </c>
       <c r="D116" s="6" t="n">
-        <v>11.07</v>
+        <v>36.38</v>
       </c>
       <c r="E116" s="6" t="n">
-        <v>6.13</v>
+        <v>1.49</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>3.05</v>
+        <v>32.89</v>
       </c>
       <c r="G116" s="6" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="H116" s="6" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="I116" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>6.65</v>
+        <v>1.49</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>3.05</v>
+        <v>32.89</v>
       </c>
       <c r="L116" s="6" t="n">
-        <v>11.6</v>
+        <v>36.38</v>
       </c>
       <c r="M116" s="6" t="n">
-        <v>12.4</v>
+        <v>-12.38</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
@@ -5872,16 +5872,16 @@
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>15.05</v>
+        <v>29.98</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>6.97</v>
+        <v>3.72</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>5.11</v>
+        <v>24.29</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2.97</v>
+        <v>1.97</v>
       </c>
       <c r="H117" s="5" t="n">
         <v>0</v>
@@ -5890,45 +5890,45 @@
         <v>0</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>6.97</v>
+        <v>3.72</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>5.11</v>
+        <v>24.29</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>15.05</v>
+        <v>29.98</v>
       </c>
       <c r="M117" s="5" t="n">
-        <v>8.949999999999999</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D118" s="6" t="n">
-        <v>32.17</v>
+        <v>27.32</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>9.98</v>
+        <v>15.74</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>18.74</v>
+        <v>5.19</v>
       </c>
       <c r="G118" s="6" t="n">
-        <v>3.44</v>
+        <v>6.39</v>
       </c>
       <c r="H118" s="6" t="n">
         <v>0</v>
@@ -5937,27 +5937,27 @@
         <v>0</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>9.98</v>
+        <v>15.74</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>18.74</v>
+        <v>5.19</v>
       </c>
       <c r="L118" s="6" t="n">
-        <v>32.17</v>
+        <v>27.32</v>
       </c>
       <c r="M118" s="6" t="n">
-        <v>-8.17</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -5966,40 +5966,40 @@
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>20.31</v>
+        <v>0</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>12.79</v>
+        <v>0</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="I119" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>12.79</v>
+        <v>4.6</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>20.31</v>
+        <v>4.6</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>3.69</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
@@ -6013,40 +6013,40 @@
         </is>
       </c>
       <c r="D120" s="6" t="n">
-        <v>9.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="G120" s="6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="H120" s="6" t="n">
-        <v>13.11</v>
+        <v>15.07</v>
       </c>
       <c r="I120" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>18.73</v>
+        <v>15.07</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="L120" s="6" t="n">
-        <v>23.07</v>
+        <v>15.07</v>
       </c>
       <c r="M120" s="6" t="n">
-        <v>0.93</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -6060,40 +6060,40 @@
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>0</v>
+        <v>34.43</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>13.29</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0</v>
+        <v>15.29</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="I121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>0.61</v>
+        <v>13.29</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0</v>
+        <v>15.29</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>0.61</v>
+        <v>34.43</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>23.39</v>
+        <v>-10.43</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
@@ -6107,85 +6107,1166 @@
         </is>
       </c>
       <c r="D122" s="6" t="n">
-        <v>15.44</v>
+        <v>13.58</v>
       </c>
       <c r="E122" s="6" t="n">
-        <v>12.56</v>
+        <v>10.51</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G122" s="6" t="n">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="H122" s="6" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="I122" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>12.56</v>
+        <v>14.72</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L122" s="6" t="n">
-        <v>15.44</v>
+        <v>17.79</v>
       </c>
       <c r="M122" s="6" t="n">
-        <v>8.56</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>3.77</v>
+        <v>20.17</v>
       </c>
       <c r="E123" s="5" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G124" s="6" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="H124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K124" s="6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L124" s="6" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="M124" s="6" t="n">
+        <v>10.65</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="M125" s="5" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G126" s="6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H126" s="6" t="n">
         <v>1.38</v>
       </c>
-      <c r="F123" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L123" s="5" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v>14.88</v>
+      <c r="I126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K126" s="6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L126" s="6" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="M126" s="6" t="n">
+        <v>7.01</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="M127" s="5" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G128" s="6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="H128" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="6" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="K128" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L128" s="6" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="M128" s="6" t="n">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="M129" s="5" t="n">
+        <v>6.98</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G130" s="6" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="H130" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="6" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="K130" s="6" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="L130" s="6" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="M130" s="6" t="n">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="M131" s="5" t="n">
+        <v>18.72</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G132" s="6" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="H132" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="6" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K132" s="6" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="L132" s="6" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="M132" s="6" t="n">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="M133" s="5" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G134" s="6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="6" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="K134" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L134" s="6" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="M134" s="6" t="n">
+        <v>14.89</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M135" s="5" t="n">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="G136" s="6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H136" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="K136" s="6" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="L136" s="6" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="M136" s="6" t="n">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="M137" s="5" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G138" s="6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H138" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K138" s="6" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="L138" s="6" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="M138" s="6" t="n">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="M139" s="5" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F140" s="6" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="G140" s="6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H140" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K140" s="6" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="L140" s="6" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="M140" s="6" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="M141" s="5" t="n">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E142" s="6" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="G142" s="6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H142" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="6" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="K142" s="6" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="L142" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M142" s="6" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="5" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="M143" s="5" t="n">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="G144" s="6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H144" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="6" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="K144" s="6" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="L144" s="6" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="M144" s="6" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="M145" s="5" t="n">
+        <v>20.15</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="G146" s="6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H146" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="6" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="K146" s="6" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="L146" s="6" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="M146" s="6" t="n">
+        <v>-3.97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M123"/>
+  <autoFilter ref="A4:M146"/>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:01</t>
+          <t>2026-08-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:33</t>
+          <t>2026-08-04 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:11</t>
+          <t>2026-08-05 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 14:34</t>
+          <t>2026-08-07 15:55</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 15:55</t>
+          <t>2026-08-09 10:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
+++ b/reports/oatside-pg-2026/exports/08_Daily_Time_24h_Check.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:57</t>
+          <t>2026-08-09 11:52</t>
         </is>
       </c>
     </row>
